--- a/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_19oct26_Mon.xlsx
+++ b/ORDER_MGMT/regular_order_mgmt/order_files/FullOrders_upto_19oct26_Mon.xlsx
@@ -1456,19 +1456,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1834,95 +1834,81 @@
       </c>
     </row>
     <row r="2" spans="1:16" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="3">
-        <v>46281.416666666664</v>
+      <c r="A2" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>267</v>
+        <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D2" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E2" s="4">
-        <v>706</v>
+        <v>2470</v>
       </c>
       <c r="F2" s="4">
-        <v>-32.691390980000001</v>
+        <v>18.368716150000001</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>272</v>
+        <v>71</v>
       </c>
       <c r="H2" s="5">
-        <v>1048.9000000000001</v>
+        <v>2086.6999999999998</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="K2" s="17" t="s">
-        <v>269</v>
-      </c>
-      <c r="L2" s="17">
-        <v>17940</v>
-      </c>
-      <c r="M2" s="17">
-        <f>ABS((D2*E2)-L2)</f>
-        <v>10880</v>
-      </c>
-      <c r="N2" s="10" t="str">
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
+      <c r="N2" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B2, $C$2:$C$636, C2, $D$2:$D$636, D2, $E$2:$E$636, E2) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O2" s="10"/>
-      <c r="P2" s="10"/>
-    </row>
-    <row r="3" spans="1:16" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="3">
-        <v>46281.416666666664</v>
+      <c r="P2" s="22"/>
+    </row>
+    <row r="3" spans="1:16" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>267</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="4">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E3" s="4">
-        <v>726</v>
+        <v>2435</v>
       </c>
       <c r="F3" s="4">
-        <v>-30.784631520000001</v>
+        <v>16.69142665</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>272</v>
+        <v>71</v>
       </c>
       <c r="H3" s="5">
-        <v>1048.9000000000001</v>
+        <v>2086.6999999999998</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="K3" s="17" t="s">
-        <v>269</v>
-      </c>
-      <c r="L3" s="17">
-        <v>17940</v>
-      </c>
-      <c r="M3" s="17">
-        <f>ABS((D3*E3)-L3)</f>
-        <v>10680</v>
-      </c>
-      <c r="N3" s="10" t="str">
+      <c r="J3" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B3, $C$2:$C$636, C3, $D$2:$D$636, D3, $E$2:$E$636, E3) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
@@ -1930,149 +1916,180 @@
       <c r="P3" s="10"/>
     </row>
     <row r="4" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" t="s">
-        <v>61</v>
+      <c r="A4" s="3">
+        <v>46275.457638888889</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>114</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="4">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="E4" s="4">
-        <v>660</v>
+        <v>222</v>
       </c>
       <c r="F4" s="4">
-        <v>-20.948616600000001</v>
+        <v>12.439222040000001</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>115</v>
+        <v>39</v>
       </c>
       <c r="H4" s="5">
-        <v>834.9</v>
+        <v>197.44</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="33" t="s">
+      <c r="J4" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" t="str">
+      <c r="K4" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="L4" s="17">
+        <v>56375</v>
+      </c>
+      <c r="M4" s="17">
+        <f>ABS((D4*E4)-L4)</f>
+        <v>34175</v>
+      </c>
+      <c r="N4" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B4, $C$2:$C$636, C4, $D$2:$D$636, D4, $E$2:$E$636, E4) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
     </row>
     <row r="5" spans="1:16" customFormat="1" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
-        <v>61</v>
+      <c r="A5" s="3">
+        <v>46261.375</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>91</v>
+        <v>23</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D5" s="4">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E5" s="4">
-        <v>2560</v>
+        <v>204</v>
       </c>
       <c r="F5" s="4">
-        <v>-19.610613910000001</v>
+        <v>12.27297744</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>92</v>
+        <v>69</v>
       </c>
       <c r="H5" s="5">
-        <v>3184.5</v>
+        <v>181.7</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J5" s="33" t="s">
+      <c r="J5" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" t="str">
+      <c r="K5" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="L5" s="17">
+        <v>10550</v>
+      </c>
+      <c r="M5" s="17">
+        <f>ABS((D5*E5)-L5)</f>
+        <v>350</v>
+      </c>
+      <c r="N5" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B5, $C$2:$C$636, C5, $D$2:$D$636, D5, $E$2:$E$636, E5) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" t="s">
-        <v>61</v>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+    </row>
+    <row r="6" spans="1:16" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="3">
+        <v>46268.385416666664</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D6" s="4">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="E6" s="4">
-        <v>2660</v>
+        <v>214</v>
       </c>
       <c r="F6" s="4">
-        <v>-16.470403520000001</v>
+        <v>8.3873581850000001</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>92</v>
+        <v>39</v>
       </c>
       <c r="H6" s="5">
-        <v>3184.5</v>
+        <v>197.44</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="33"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" s="16"/>
-      <c r="N6" t="str">
+      <c r="J6" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="L6" s="17">
+        <v>21900</v>
+      </c>
+      <c r="M6" s="17">
+        <f>ABS((D6*E6)-L6)</f>
+        <v>500</v>
+      </c>
+      <c r="N6" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B6, $C$2:$C$636, C6, $D$2:$D$636, D6, $E$2:$E$636, E6) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
     </row>
     <row r="7" spans="1:16" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="4">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E7" s="4">
-        <v>4014</v>
+        <v>212</v>
       </c>
       <c r="F7" s="4">
-        <v>-14.595744679999999</v>
+        <v>7.3743922199999998</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>97</v>
+        <v>39</v>
       </c>
       <c r="H7" s="5">
-        <v>4700</v>
+        <v>197.44</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="33"/>
+      <c r="J7" s="33" t="s">
+        <v>40</v>
+      </c>
       <c r="K7" s="16"/>
       <c r="L7" s="16"/>
       <c r="M7" s="16"/>
@@ -2080,145 +2097,126 @@
         <f>IF(COUNTIFS( $B$2:$B$636, B7, $C$2:$C$636, C7, $D$2:$D$636, D7, $E$2:$E$636, E7) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
     </row>
     <row r="8" spans="1:16" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
-        <v>46031.4375</v>
+        <v>46252.645138888889</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>204</v>
+        <v>67</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="4">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E8" s="4">
-        <v>1052</v>
+        <v>401</v>
       </c>
       <c r="F8" s="4">
-        <v>-14.464590619999999</v>
+        <v>6.3096500530000004</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>215</v>
+        <v>68</v>
       </c>
       <c r="H8" s="5">
-        <v>1229.9000000000001</v>
+        <v>377.2</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J8" s="21" t="s">
+      <c r="J8" s="67" t="s">
         <v>40</v>
       </c>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17">
-        <f>ABS((D8*E8)-L8)</f>
-        <v>3156</v>
-      </c>
-      <c r="N8" s="10" t="str">
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="16"/>
+      <c r="N8" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B8, $C$2:$C$636, C8, $D$2:$D$636, D8, $E$2:$E$636, E8) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O8" s="10"/>
-      <c r="P8" s="18"/>
+      <c r="P8" s="10"/>
     </row>
     <row r="9" spans="1:16" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="42">
-        <v>46304.388888888891</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="A9" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="5">
-        <v>9</v>
-      </c>
-      <c r="E9" s="5">
-        <v>2105</v>
+      <c r="D9" s="4">
+        <v>5</v>
+      </c>
+      <c r="E9" s="4">
+        <v>3888</v>
       </c>
       <c r="F9" s="4">
-        <v>-14.46218863</v>
+        <v>6.1743903439999999</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H9" s="5">
-        <v>2460.9</v>
+        <v>3661.9</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J9" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="K9" s="17" t="s">
-        <v>308</v>
-      </c>
-      <c r="L9" s="17">
-        <v>19395</v>
-      </c>
-      <c r="M9" s="17">
-        <f>ABS((D9*E9)-L9)</f>
-        <v>450</v>
-      </c>
+      <c r="J9" s="33"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="16"/>
       <c r="N9" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B9, $C$2:$C$636, C9, $D$2:$D$636, D9, $E$2:$E$636, E9) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O9" s="10"/>
+      <c r="O9" s="23"/>
       <c r="P9" s="10"/>
     </row>
     <row r="10" spans="1:16" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="42">
-        <v>46311.375</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="A10" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="5">
-        <v>5</v>
-      </c>
-      <c r="E10" s="5">
-        <v>640</v>
+      <c r="D10" s="4">
+        <v>2</v>
+      </c>
+      <c r="E10" s="4">
+        <v>3856</v>
       </c>
       <c r="F10" s="4">
-        <v>-14.09395973</v>
+        <v>5.3005270490000003</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="H10" s="5">
-        <v>745</v>
+        <v>3661.9</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J10" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="K10" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="L10" s="17">
-        <v>3450</v>
-      </c>
-      <c r="M10" s="17">
-        <f>ABS((D10*E10)-L10)</f>
-        <v>250</v>
-      </c>
-      <c r="N10" s="10" t="str">
+      <c r="J10" s="33"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="16"/>
+      <c r="N10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B10, $C$2:$C$636, C10, $D$2:$D$636, D10, $E$2:$E$636, E10) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O10" s="10"/>
+      <c r="O10" s="18"/>
       <c r="P10" s="10"/>
     </row>
     <row r="11" spans="1:16" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2226,32 +2224,30 @@
         <v>61</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D11" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="4">
-        <v>2752</v>
+        <v>3830</v>
       </c>
       <c r="F11" s="4">
-        <v>-13.581409949999999</v>
+        <v>4.5905131219999999</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="H11" s="5">
-        <v>3184.5</v>
+        <v>3661.9</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J11" s="33" t="s">
-        <v>40</v>
-      </c>
+      <c r="J11" s="33"/>
       <c r="K11" s="16"/>
       <c r="L11" s="16"/>
       <c r="M11" s="16"/>
@@ -2259,176 +2255,155 @@
         <f>IF(COUNTIFS( $B$2:$B$636, B11, $C$2:$C$636, C11, $D$2:$D$636, D11, $E$2:$E$636, E11) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
+      <c r="O11" s="10"/>
+      <c r="P11" s="10"/>
     </row>
     <row r="12" spans="1:16" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="42">
-        <v>46304.387499999997</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="A12" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="5">
-        <v>500</v>
-      </c>
-      <c r="E12" s="5">
-        <v>30.3</v>
+      <c r="D12" s="4">
+        <v>50</v>
+      </c>
+      <c r="E12" s="4">
+        <v>206</v>
       </c>
       <c r="F12" s="4">
-        <v>-13.23024055</v>
+        <v>4.3354943270000001</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="H12" s="5">
-        <v>34.92</v>
+        <v>197.44</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J12" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="K12" s="17" t="s">
-        <v>304</v>
-      </c>
-      <c r="L12" s="17">
-        <v>15850</v>
-      </c>
-      <c r="M12" s="17">
-        <f>ABS((D12*E12)-L12)</f>
-        <v>700</v>
-      </c>
+      <c r="J12" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
       <c r="N12" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B12, $C$2:$C$636, C12, $D$2:$D$636, D12, $E$2:$E$636, E12) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
     </row>
     <row r="13" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="42">
-        <v>46308.538888888892</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="A13" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="5">
-        <v>8</v>
-      </c>
-      <c r="E13" s="5">
-        <v>2155</v>
+      <c r="D13" s="4">
+        <v>3</v>
+      </c>
+      <c r="E13" s="4">
+        <v>3810</v>
       </c>
       <c r="F13" s="4">
-        <v>-12.430411640000001</v>
+        <v>4.0443485619999997</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H13" s="5">
-        <v>2460.9</v>
+        <v>3661.9</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J13" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="K13" s="17" t="s">
-        <v>317</v>
-      </c>
-      <c r="L13" s="17">
-        <v>18040</v>
-      </c>
-      <c r="M13" s="17">
-        <f>ABS((D13*E13)-L13)</f>
-        <v>800</v>
-      </c>
+      <c r="J13" s="33"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
       <c r="N13" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B13, $C$2:$C$636, C13, $D$2:$D$636, D13, $E$2:$E$636, E13) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="42">
-        <v>46308.578472222223</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="A14" s="3">
+        <v>46252.635416666664</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="5">
-        <v>13</v>
-      </c>
-      <c r="E14" s="5">
-        <v>1209</v>
+      <c r="D14" s="4">
+        <v>3</v>
+      </c>
+      <c r="E14" s="4">
+        <v>1302</v>
       </c>
       <c r="F14" s="4">
-        <v>-12.38495543</v>
+        <v>2.5196850390000001</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>321</v>
+        <v>78</v>
       </c>
       <c r="H14" s="5">
-        <v>1379.9</v>
+        <v>1270</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="K14" s="17" t="s">
-        <v>316</v>
-      </c>
-      <c r="L14" s="17">
-        <v>17017</v>
-      </c>
-      <c r="M14" s="17">
-        <f>ABS((D14*E14)-L14)</f>
-        <v>1300</v>
-      </c>
+      <c r="J14" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="16"/>
       <c r="N14" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B14, $C$2:$C$636, C14, $D$2:$D$636, D14, $E$2:$E$636, E14) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
+      <c r="O14"/>
+      <c r="P14"/>
     </row>
     <row r="15" spans="1:16" ht="15" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="6" t="s">
-        <v>61</v>
+      <c r="A15" s="3">
+        <v>46252.6875</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="4">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="E15" s="4">
-        <v>701</v>
+        <v>122</v>
       </c>
       <c r="F15" s="4">
-        <v>-11.71284635</v>
+        <v>1.8193957599999999</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="H15" s="5">
-        <v>794</v>
+        <v>119.82</v>
       </c>
       <c r="I15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J15" s="33" t="s">
+      <c r="J15" s="34" t="s">
         <v>40</v>
       </c>
       <c r="K15" s="16"/>
@@ -2438,49 +2413,47 @@
         <f>IF(COUNTIFS( $B$2:$B$636, B15, $C$2:$C$636, C15, $D$2:$D$636, D15, $E$2:$E$636, E15) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O15"/>
-      <c r="P15"/>
-    </row>
-    <row r="16" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="42">
-        <v>46311.375</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="2" t="s">
+    </row>
+    <row r="16" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="3">
+        <v>46283.375</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="5">
-        <v>5</v>
-      </c>
-      <c r="E16" s="5">
-        <v>660</v>
+      <c r="D16" s="4">
+        <v>20</v>
+      </c>
+      <c r="E16" s="4">
+        <v>870.2</v>
       </c>
       <c r="F16" s="4">
-        <v>-11.40939597</v>
+        <v>1.7777777779999999</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="H16" s="5">
-        <v>745</v>
+        <v>855</v>
       </c>
       <c r="I16" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J16" s="21" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="K16" s="17" t="s">
-        <v>328</v>
+        <v>274</v>
       </c>
       <c r="L16" s="17">
-        <v>3550</v>
+        <v>17920</v>
       </c>
       <c r="M16" s="17">
         <f>ABS((D16*E16)-L16)</f>
-        <v>250</v>
+        <v>516</v>
       </c>
       <c r="N16" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B16, $C$2:$C$636, C16, $D$2:$D$636, D16, $E$2:$E$636, E16) &gt; 1, "Duplicate", "Unique")</f>
@@ -2488,77 +2461,89 @@
       </c>
     </row>
     <row r="17" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="6" t="s">
-        <v>61</v>
+      <c r="A17" s="3">
+        <v>46261.375</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D17" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E17" s="4">
-        <v>4164</v>
+        <v>870</v>
       </c>
       <c r="F17" s="4">
-        <v>-11.404255320000001</v>
+        <v>1.754385965</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
       <c r="H17" s="5">
-        <v>4700</v>
+        <v>855</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J17" s="33"/>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" t="str">
+      <c r="J17" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="K17" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="L17" s="17">
+        <v>17700</v>
+      </c>
+      <c r="M17" s="17">
+        <f>ABS((D17*E17)-L17)</f>
+        <v>300</v>
+      </c>
+      <c r="N17" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B17, $C$2:$C$636, C17, $D$2:$D$636, D17, $E$2:$E$636, E17) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O17"/>
-      <c r="P17"/>
-    </row>
-    <row r="18" spans="1:16" s="22" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="6" t="s">
-        <v>61</v>
+      <c r="P17" s="22"/>
+    </row>
+    <row r="18" spans="1:16" s="22" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="3">
+        <v>46254.375</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>108</v>
+        <v>32</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="4">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E18" s="4">
-        <v>4415</v>
+        <v>2230</v>
       </c>
       <c r="F18" s="4">
-        <v>-10.96995362</v>
+        <v>0.8958465297</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="H18" s="5">
-        <v>4959</v>
+        <v>2210.1999999999998</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J18" s="33"/>
-      <c r="K18" s="16"/>
+      <c r="J18" s="68" t="s">
+        <v>54</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>146</v>
+      </c>
       <c r="L18" s="16"/>
       <c r="M18" s="16"/>
-      <c r="N18" t="str">
+      <c r="N18" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B18, $C$2:$C$636, C18, $D$2:$D$636, D18, $E$2:$E$636, E18) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
@@ -2566,80 +2551,75 @@
       <c r="P18"/>
     </row>
     <row r="19" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="42">
-        <v>46308.536805555559</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="2" t="s">
+      <c r="A19" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="5">
-        <v>200</v>
-      </c>
-      <c r="E19" s="5">
-        <v>31.1</v>
+      <c r="D19" s="4">
+        <v>69</v>
+      </c>
+      <c r="E19" s="4">
+        <v>1277</v>
       </c>
       <c r="F19" s="4">
-        <v>-10.93928981</v>
+        <v>0.55118110239999996</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="H19" s="5">
-        <v>34.92</v>
+        <v>1270</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J19" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="K19" s="17" t="s">
-        <v>318</v>
-      </c>
-      <c r="L19" s="17">
-        <v>6580</v>
-      </c>
-      <c r="M19" s="17">
-        <f>ABS((D19*E19)-L19)</f>
-        <v>360</v>
-      </c>
+      <c r="J19" s="33"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="16"/>
       <c r="N19" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B19, $C$2:$C$636, C19, $D$2:$D$636, D19, $E$2:$E$636, E19) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="6" t="s">
-        <v>61</v>
+      <c r="O19"/>
+      <c r="P19"/>
+    </row>
+    <row r="20" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="3">
+        <v>46252.635416666664</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>108</v>
+        <v>31</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D20" s="4">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="E20" s="4">
-        <v>4456</v>
+        <v>850</v>
       </c>
       <c r="F20" s="4">
-        <v>-10.143174030000001</v>
+        <v>-0.58479532160000003</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="H20" s="5">
-        <v>4959</v>
+        <v>855</v>
       </c>
       <c r="I20" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J20" s="33"/>
+      <c r="J20" s="34" t="s">
+        <v>54</v>
+      </c>
       <c r="K20" s="16"/>
       <c r="L20" s="16"/>
       <c r="M20" s="16"/>
@@ -2647,84 +2627,77 @@
         <f>IF(COUNTIFS( $B$2:$B$636, B20, $C$2:$C$636, C20, $D$2:$D$636, D20, $E$2:$E$636, E20) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O20"/>
       <c r="P20"/>
     </row>
     <row r="21" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="42">
-        <v>46303.375</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="C21" s="2" t="s">
+      <c r="A21" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="5">
-        <v>2</v>
-      </c>
-      <c r="E21" s="5">
-        <v>1294</v>
+      <c r="D21" s="4">
+        <v>50</v>
+      </c>
+      <c r="E21" s="4">
+        <v>119</v>
       </c>
       <c r="F21" s="4">
-        <v>-9.9199443089999999</v>
+        <v>-0.68435987310000002</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>275</v>
+        <v>85</v>
       </c>
       <c r="H21" s="5">
-        <v>1436.5</v>
+        <v>119.82</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J21" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="K21" s="17" t="s">
-        <v>301</v>
-      </c>
-      <c r="L21" s="17">
-        <v>2852</v>
-      </c>
-      <c r="M21" s="17">
-        <f>ABS((D21*E21)-L21)</f>
-        <v>264</v>
-      </c>
-      <c r="N21" s="10" t="str">
+      <c r="J21" s="33"/>
+      <c r="K21" s="16"/>
+      <c r="L21" s="16"/>
+      <c r="M21" s="16"/>
+      <c r="N21" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B21, $C$2:$C$636, C21, $D$2:$D$636, D21, $E$2:$E$636, E21) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
+      <c r="O21"/>
     </row>
     <row r="22" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="3">
-        <v>46252.635416666664</v>
+      <c r="A22" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>91</v>
+        <v>18</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D22" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E22" s="4">
-        <v>2892</v>
+        <v>1614</v>
       </c>
       <c r="F22" s="4">
-        <v>-9.1851154029999993</v>
+        <v>-0.71968997970000004</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="H22" s="5">
-        <v>3184.5</v>
+        <v>1625.7</v>
       </c>
       <c r="I22" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J22" s="33"/>
+      <c r="J22" s="69" t="s">
+        <v>40</v>
+      </c>
       <c r="K22" s="16"/>
       <c r="L22" s="16"/>
       <c r="M22" s="16"/>
@@ -2735,228 +2708,239 @@
       <c r="O22"/>
       <c r="P22"/>
     </row>
-    <row r="23" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="42">
-        <v>46289.375</v>
+        <v>46304.375</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D23" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E23" s="5">
-        <v>601</v>
+        <v>1708.7</v>
       </c>
       <c r="F23" s="4">
-        <v>-8.9600848289999995</v>
+        <v>-0.77235772359999999</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="H23" s="5">
-        <v>660.15</v>
+        <v>1722</v>
       </c>
       <c r="I23" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J23" s="21" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="K23" s="17" t="s">
-        <v>280</v>
+        <v>309</v>
       </c>
       <c r="L23" s="17">
-        <v>3245</v>
+        <v>17487</v>
       </c>
       <c r="M23" s="17">
         <f>ABS((D23*E23)-L23)</f>
-        <v>240</v>
-      </c>
-      <c r="N23" s="10" t="str">
+        <v>400</v>
+      </c>
+      <c r="N23" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B23, $C$2:$C$636, C23, $D$2:$D$636, D23, $E$2:$E$636, E23) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="1" t="s">
+    <row r="24" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="42">
+        <v>46308.620138888888</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="E24" s="4">
-        <v>18052</v>
+      <c r="D24" s="5">
+        <v>10</v>
+      </c>
+      <c r="E24" s="5">
+        <v>3310</v>
       </c>
       <c r="F24" s="4">
-        <v>-8.8420946320000002</v>
+        <v>-0.77937649880000004</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H24" s="5">
-        <v>19803</v>
+        <v>3336</v>
       </c>
       <c r="I24" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J24" s="33"/>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
+      <c r="J24" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="K24" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="L24" s="17">
+        <v>33800</v>
+      </c>
+      <c r="M24" s="17">
+        <f>ABS((D24*E24)-L24)</f>
+        <v>700</v>
+      </c>
       <c r="N24" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B24, $C$2:$C$636, C24, $D$2:$D$636, D24, $E$2:$E$636, E24) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O24"/>
-      <c r="P24"/>
-    </row>
-    <row r="25" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="42">
         <v>46314.37537037037</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D25" s="5">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E25" s="5">
-        <v>680</v>
+        <v>336</v>
       </c>
       <c r="F25" s="4">
-        <v>-8.7248322149999993</v>
+        <v>-1.1764705879999999</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H25" s="5">
-        <v>745</v>
+        <v>340</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>8</v>
       </c>
       <c r="J25" s="21" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="K25" s="17" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="L25" s="17">
-        <v>3650</v>
+        <v>8700</v>
       </c>
       <c r="M25" s="17">
         <f>ABS((D25*E25)-L25)</f>
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="N25" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B25, $C$2:$C$636, C25, $D$2:$D$636, D25, $E$2:$E$636, E25) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="42">
-        <v>46310.40347222222</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C26" s="2" t="s">
+    <row r="26" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="59" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="50" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="5">
-        <v>300</v>
-      </c>
-      <c r="E26" s="5">
-        <v>32.01</v>
+      <c r="D26" s="51">
+        <v>40</v>
+      </c>
+      <c r="E26" s="51">
+        <v>862</v>
       </c>
       <c r="F26" s="4">
-        <v>-8.3333333330000006</v>
+        <v>-1.2090997649999999</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H26" s="5">
-        <v>34.92</v>
+        <v>872.55</v>
       </c>
       <c r="I26" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J26" s="21" t="s">
+      <c r="J26" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="K26" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="L26" s="17">
-        <v>10263</v>
-      </c>
-      <c r="M26" s="17">
-        <f>ABS((D26*E26)-L26)</f>
-        <v>660</v>
-      </c>
-      <c r="N26" s="10" t="str">
+      <c r="K26" s="60"/>
+      <c r="L26" s="60"/>
+      <c r="M26" s="60"/>
+      <c r="N26" s="52" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B26, $C$2:$C$636, C26, $D$2:$D$636, D26, $E$2:$E$636, E26) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
+      <c r="O26" s="52"/>
+      <c r="P26" s="52"/>
     </row>
     <row r="27" spans="1:16" s="22" customFormat="1" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C27" s="1" t="s">
+      <c r="A27" s="42">
+        <v>46301.393055555556</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="4">
+      <c r="D27" s="5">
         <v>1</v>
       </c>
-      <c r="E27" s="4">
-        <v>4560</v>
+      <c r="E27" s="5">
+        <v>19550</v>
       </c>
       <c r="F27" s="4">
-        <v>-8.0459770109999997</v>
+        <v>-1.2775842040000001</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="H27" s="5">
-        <v>4959</v>
+        <v>19803</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J27" s="33"/>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" s="16"/>
-      <c r="N27" t="str">
+      <c r="J27" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="K27" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="L27" s="17">
+        <v>20020</v>
+      </c>
+      <c r="M27" s="17">
+        <f>ABS((D27*E27)-L27)</f>
+        <v>470</v>
+      </c>
+      <c r="N27" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B27, $C$2:$C$636, C27, $D$2:$D$636, D27, $E$2:$E$636, E27) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O27"/>
-      <c r="P27"/>
-    </row>
-    <row r="28" spans="1:16" ht="40.799999999999997" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O27" s="10"/>
+      <c r="P27" s="10"/>
+    </row>
+    <row r="28" spans="1:16" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
-        <v>46286.375</v>
+        <v>46307.375</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>10</v>
@@ -2965,33 +2949,32 @@
         <v>5</v>
       </c>
       <c r="E28" s="4">
-        <v>702</v>
+        <v>3288</v>
       </c>
       <c r="F28" s="4">
-        <v>-7.6315789470000004</v>
+        <v>-1.4388489209999999</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="H28" s="5">
-        <v>760</v>
+        <v>3336</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J28" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="K28" s="17" t="s">
-        <v>276</v>
-      </c>
-      <c r="L28" s="17">
-        <f>7470/2</f>
-        <v>3735</v>
+      <c r="J28" s="71" t="s">
+        <v>54</v>
+      </c>
+      <c r="K28" t="s">
+        <v>313</v>
+      </c>
+      <c r="L28">
+        <v>16740</v>
       </c>
       <c r="M28" s="17">
         <f>ABS((D28*E28)-L28)</f>
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="N28" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B28, $C$2:$C$636, C28, $D$2:$D$636, D28, $E$2:$E$636, E28) &gt; 1, "Duplicate", "Unique")</f>
@@ -3003,30 +2986,32 @@
         <v>61</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>20</v>
+        <v>81</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D29" s="4">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="E29" s="4">
-        <v>111</v>
+        <v>4010</v>
       </c>
       <c r="F29" s="4">
-        <v>-7.3610415619999996</v>
+        <v>-1.5709376530000001</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="H29" s="5">
-        <v>119.82</v>
+        <v>4074</v>
       </c>
       <c r="I29" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J29" s="33"/>
+      <c r="J29" s="33" t="s">
+        <v>40</v>
+      </c>
       <c r="K29" s="16"/>
       <c r="L29" s="16"/>
       <c r="M29" s="16"/>
@@ -3034,74 +3019,79 @@
         <f>IF(COUNTIFS( $B$2:$B$636, B29, $C$2:$C$636, C29, $D$2:$D$636, D29, $E$2:$E$636, E29) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O29"/>
-      <c r="P29"/>
-    </row>
-    <row r="30" spans="1:16" s="27" customFormat="1" ht="14.4" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C30" s="1" t="s">
+    </row>
+    <row r="30" spans="1:16" s="27" customFormat="1" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="42">
+        <v>46310.375</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D30" s="4">
-        <v>1</v>
-      </c>
-      <c r="E30" s="4">
-        <v>4364</v>
+      <c r="D30" s="5">
+        <v>100</v>
+      </c>
+      <c r="E30" s="5">
+        <v>315.10000000000002</v>
       </c>
       <c r="F30" s="4">
-        <v>-7.1489361699999998</v>
+        <v>-1.7155333749999999</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>97</v>
+        <v>44</v>
       </c>
       <c r="H30" s="5">
-        <v>4700</v>
+        <v>320.60000000000002</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J30" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" s="16"/>
-      <c r="N30" t="str">
+      <c r="J30" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="K30" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="L30" s="17">
+        <v>32200</v>
+      </c>
+      <c r="M30" s="17">
+        <f>ABS((D30*E30)-L30)</f>
+        <v>689.99999999999636</v>
+      </c>
+      <c r="N30" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B30, $C$2:$C$636, C30, $D$2:$D$636, D30, $E$2:$E$636, E30) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O30"/>
-      <c r="P30"/>
+      <c r="O30" s="10"/>
+      <c r="P30" s="10"/>
     </row>
     <row r="31" spans="1:16" s="26" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="3">
-        <v>46302.468055555553</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C31" s="1" t="s">
+      <c r="A31" s="42">
+        <v>46311.375</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D31" s="4">
-        <v>2</v>
-      </c>
-      <c r="E31" s="4">
-        <v>3110</v>
+      <c r="D31" s="5">
+        <v>5</v>
+      </c>
+      <c r="E31" s="5">
+        <v>746</v>
       </c>
       <c r="F31" s="4">
-        <v>-6.7745803359999996</v>
+        <v>-1.8421052630000001</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="H31" s="5">
-        <v>3336</v>
+        <v>760</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>8</v>
@@ -3110,15 +3100,15 @@
         <v>40</v>
       </c>
       <c r="K31" s="17" t="s">
-        <v>298</v>
+        <v>331</v>
       </c>
       <c r="L31" s="17">
-        <f>2*3334</f>
-        <v>6668</v>
+        <f>5*773</f>
+        <v>3865</v>
       </c>
       <c r="M31" s="17">
         <f>ABS((D31*E31)-L31)</f>
-        <v>448</v>
+        <v>135</v>
       </c>
       <c r="N31" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B31, $C$2:$C$636, C31, $D$2:$D$636, D31, $E$2:$E$636, E31) &gt; 1, "Duplicate", "Unique")</f>
@@ -3128,45 +3118,46 @@
       <c r="P31" s="10"/>
     </row>
     <row r="32" spans="1:16" s="26" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="62">
-        <v>46309</v>
+      <c r="A32" s="42">
+        <v>46311.595833333333</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>108</v>
+        <v>11</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D32" s="5">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E32" s="5">
-        <v>4640</v>
+        <v>271</v>
       </c>
       <c r="F32" s="4">
-        <v>-6.4327485380000002</v>
+        <v>-1.9891500900000001</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="H32" s="5">
-        <v>4959</v>
+        <v>276.5</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J32" s="64" t="s">
+      <c r="J32" s="17" t="s">
         <v>40</v>
       </c>
       <c r="K32" s="17" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="L32" s="17">
-        <v>4940</v>
+        <f>20*283</f>
+        <v>5660</v>
       </c>
       <c r="M32" s="17">
         <f>ABS((D32*E32)-L32)</f>
-        <v>300</v>
+        <v>240</v>
       </c>
       <c r="N32" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B32, $C$2:$C$636, C32, $D$2:$D$636, D32, $E$2:$E$636, E32) &gt; 1, "Duplicate", "Unique")</f>
@@ -3180,7 +3171,7 @@
         <v>61</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>99</v>
+        <v>31</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>10</v>
@@ -3189,16 +3180,16 @@
         <v>25</v>
       </c>
       <c r="E33" s="4">
-        <v>251</v>
+        <v>836</v>
       </c>
       <c r="F33" s="4">
-        <v>-6.4305684999999997</v>
+        <v>-2.2222222220000001</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="H33" s="5">
-        <v>268.25</v>
+        <v>855</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>8</v>
@@ -3216,273 +3207,276 @@
       <c r="O33"/>
       <c r="P33"/>
     </row>
-    <row r="34" spans="1:16" customFormat="1" ht="40.799999999999997" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="6" t="s">
+    <row r="34" spans="1:16" customFormat="1" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="45">
+        <v>46304.375</v>
+      </c>
+      <c r="B34" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="D34" s="47">
+        <v>10</v>
+      </c>
+      <c r="E34" s="47">
+        <v>852</v>
+      </c>
+      <c r="F34" s="4">
+        <v>-2.3551658930000001</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H34" s="5">
+        <v>872.55</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J34" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="K34" s="25" t="s">
+        <v>310</v>
+      </c>
+      <c r="L34" s="25">
+        <v>8570</v>
+      </c>
+      <c r="M34" s="25">
+        <f>ABS((D34*E34)-L34)</f>
+        <v>50</v>
+      </c>
+      <c r="N34" s="26" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$636, B34, $C$2:$C$636, C34, $D$2:$D$636, D34, $E$2:$E$636, E34) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Duplicate</v>
+      </c>
+      <c r="O34" s="27"/>
+      <c r="P34" s="27"/>
+    </row>
+    <row r="35" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A35" s="28">
+        <v>46307.375</v>
+      </c>
+      <c r="B35" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C35" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="D35" s="30">
+        <v>10</v>
+      </c>
+      <c r="E35" s="30">
+        <v>852</v>
+      </c>
+      <c r="F35" s="4">
+        <v>-2.3551658930000001</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H35" s="5">
+        <v>872.55</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J35" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="K35" s="26" t="s">
+        <v>312</v>
+      </c>
+      <c r="L35" s="26">
+        <v>8670</v>
+      </c>
+      <c r="M35" s="25">
+        <f>ABS((D35*E35)-L35)</f>
+        <v>150</v>
+      </c>
+      <c r="N35" s="27" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$636, B35, $C$2:$C$636, C35, $D$2:$D$636, D35, $E$2:$E$636, E35) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Duplicate</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" s="53" customFormat="1" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A36" s="45">
+        <v>46308.375</v>
+      </c>
+      <c r="B36" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="C36" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="D36" s="47">
+        <v>10</v>
+      </c>
+      <c r="E36" s="47">
+        <v>852</v>
+      </c>
+      <c r="F36" s="4">
+        <v>-2.3551658930000001</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H36" s="5">
+        <v>872.55</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J36" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="K36" s="25" t="s">
+        <v>319</v>
+      </c>
+      <c r="L36" s="25">
+        <v>8870</v>
+      </c>
+      <c r="M36" s="25">
+        <f>ABS((D36*E36)-L36)</f>
+        <v>350</v>
+      </c>
+      <c r="N36" s="26" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$636, B36, $C$2:$C$636, C36, $D$2:$D$636, D36, $E$2:$E$636, E36) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Duplicate</v>
+      </c>
+      <c r="O36" s="27"/>
+      <c r="P36" s="27"/>
+    </row>
+    <row r="37" spans="1:16" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="45">
+        <v>46308.375</v>
+      </c>
+      <c r="B37" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="C37" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="D37" s="47">
+        <v>10</v>
+      </c>
+      <c r="E37" s="47">
+        <v>852</v>
+      </c>
+      <c r="F37" s="4">
+        <v>-2.3551658930000001</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H37" s="5">
+        <v>872.55</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J37" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="K37" s="25" t="s">
+        <v>320</v>
+      </c>
+      <c r="L37" s="25">
+        <v>8770</v>
+      </c>
+      <c r="M37" s="25">
+        <f>ABS((D37*E37)-L37)</f>
+        <v>250</v>
+      </c>
+      <c r="N37" s="26" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$636, B37, $C$2:$C$636, C37, $D$2:$D$636, D37, $E$2:$E$636, E37) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Duplicate</v>
+      </c>
+      <c r="O37" s="27"/>
+      <c r="P37" s="27"/>
+    </row>
+    <row r="38" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C34" s="1" t="s">
+      <c r="B38" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D34" s="4">
-        <v>1</v>
-      </c>
-      <c r="E34" s="4">
-        <v>18552</v>
-      </c>
-      <c r="F34" s="4">
-        <v>-6.3172246630000002</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H34" s="5">
-        <v>19803</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J34" s="65"/>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B34, $C$2:$C$636, C34, $D$2:$D$636, D34, $E$2:$E$636, E34) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="42">
-        <v>46311.375</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D35" s="5">
-        <v>5</v>
-      </c>
-      <c r="E35" s="5">
-        <v>712</v>
-      </c>
-      <c r="F35" s="4">
-        <v>-6.3157894739999998</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H35" s="5">
-        <v>760</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J35" s="64" t="s">
-        <v>40</v>
-      </c>
-      <c r="K35" s="17" t="s">
-        <v>329</v>
-      </c>
-      <c r="L35" s="17">
-        <v>3810</v>
-      </c>
-      <c r="M35" s="17">
-        <f>ABS((D35*E35)-L35)</f>
-        <v>250</v>
-      </c>
-      <c r="N35" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B35, $C$2:$C$636, C35, $D$2:$D$636, D35, $E$2:$E$636, E35) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O35" s="10"/>
-      <c r="P35" s="10"/>
-    </row>
-    <row r="36" spans="1:16" s="53" customFormat="1" ht="40.799999999999997" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="3">
-        <v>46121.375</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D36" s="4">
-        <v>3</v>
-      </c>
-      <c r="E36" s="4">
-        <v>1614</v>
-      </c>
-      <c r="F36" s="4">
-        <v>-6.2717770030000004</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H36" s="5">
-        <v>1722</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J36" s="64" t="s">
-        <v>40</v>
-      </c>
-      <c r="K36" s="17" t="s">
-        <v>234</v>
-      </c>
-      <c r="L36" s="17">
-        <f>3*1794</f>
-        <v>5382</v>
-      </c>
-      <c r="M36" s="17">
-        <f>ABS((D36*E36)-L36)</f>
-        <v>540</v>
-      </c>
-      <c r="N36" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B36, $C$2:$C$636, C36, $D$2:$D$636, D36, $E$2:$E$636, E36) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O36"/>
-      <c r="P36"/>
-    </row>
-    <row r="37" spans="1:16" ht="27.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="42">
-        <v>46295.375</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="5">
-        <v>5</v>
-      </c>
-      <c r="E37" s="5">
-        <v>620</v>
-      </c>
-      <c r="F37" s="4">
-        <v>-6.0819510719999998</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="H37" s="5">
-        <v>660.15</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J37" s="64" t="s">
-        <v>40</v>
-      </c>
-      <c r="K37" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="L37" s="17">
-        <v>3395</v>
-      </c>
-      <c r="M37" s="17">
-        <f>ABS((D37*E37)-L37)</f>
-        <v>295</v>
-      </c>
-      <c r="N37" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B37, $C$2:$C$636, C37, $D$2:$D$636, D37, $E$2:$E$636, E37) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="42">
-        <v>46314.375648148147</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D38" s="5">
-        <v>11</v>
-      </c>
-      <c r="E38" s="5">
-        <v>701</v>
+      <c r="D38" s="4">
+        <v>50</v>
+      </c>
+      <c r="E38" s="4">
+        <v>116</v>
       </c>
       <c r="F38" s="4">
-        <v>-5.9060402679999999</v>
+        <v>-3.188115507</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="H38" s="5">
-        <v>745</v>
+        <v>119.82</v>
       </c>
       <c r="I38" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J38" s="17" t="s">
-        <v>349</v>
-      </c>
-      <c r="K38" s="17" t="s">
-        <v>346</v>
-      </c>
-      <c r="L38" s="17">
-        <v>8239</v>
-      </c>
-      <c r="M38" s="17">
-        <f>ABS((D38*E38)-L38)</f>
-        <v>528</v>
-      </c>
+      <c r="J38" s="43"/>
+      <c r="K38" s="16"/>
+      <c r="L38" s="16"/>
+      <c r="M38" s="16"/>
       <c r="N38" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B38, $C$2:$C$636, C38, $D$2:$D$636, D38, $E$2:$E$636, E38) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
+      <c r="O38"/>
+      <c r="P38"/>
     </row>
     <row r="39" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="42">
-        <v>46311.595833333333</v>
+        <v>46301.375694444447</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D39" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E39" s="5">
-        <v>261</v>
+        <v>1664</v>
       </c>
       <c r="F39" s="4">
-        <v>-5.6057866179999998</v>
+        <v>-3.3681765389999998</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="H39" s="5">
-        <v>276.5</v>
+        <v>1722</v>
       </c>
       <c r="I39" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J39" s="64" t="s">
+      <c r="J39" s="17" t="s">
         <v>40</v>
       </c>
       <c r="K39" s="17" t="s">
-        <v>333</v>
+        <v>296</v>
       </c>
       <c r="L39" s="17">
-        <f>10*283</f>
-        <v>2830</v>
+        <f>5*1752</f>
+        <v>8760</v>
       </c>
       <c r="M39" s="17">
         <f>ABS((D39*E39)-L39)</f>
-        <v>220</v>
+        <v>440</v>
       </c>
       <c r="N39" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B39, $C$2:$C$636, C39, $D$2:$D$636, D39, $E$2:$E$636, E39) &gt; 1, "Duplicate", "Unique")</f>
@@ -3490,83 +3484,75 @@
       </c>
     </row>
     <row r="40" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="42">
-        <v>46311.375</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C40" s="2" t="s">
+      <c r="A40" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D40" s="5">
-        <v>5</v>
-      </c>
-      <c r="E40" s="5">
-        <v>726</v>
+      <c r="D40" s="4">
+        <v>200</v>
+      </c>
+      <c r="E40" s="4">
+        <v>115.25</v>
       </c>
       <c r="F40" s="4">
-        <v>-4.4736842110000001</v>
+        <v>-3.8140544150000002</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="H40" s="5">
-        <v>760</v>
+        <v>119.82</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J40" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="K40" s="17" t="s">
-        <v>331</v>
-      </c>
-      <c r="L40" s="17">
-        <f>5*773</f>
-        <v>3865</v>
-      </c>
-      <c r="M40" s="17">
-        <f>ABS((D40*E40)-L40)</f>
-        <v>235</v>
-      </c>
-      <c r="N40" s="10" t="str">
+      <c r="J40" s="43"/>
+      <c r="K40" s="16"/>
+      <c r="L40" s="16"/>
+      <c r="M40" s="16"/>
+      <c r="N40" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B40, $C$2:$C$636, C40, $D$2:$D$636, D40, $E$2:$E$636, E40) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O40" s="10"/>
-      <c r="P40" s="10"/>
-    </row>
-    <row r="41" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="6" t="s">
-        <v>61</v>
+      <c r="O40"/>
+      <c r="P40"/>
+    </row>
+    <row r="41" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="3">
+        <v>46252.688194444447</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D41" s="4">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="E41" s="4">
-        <v>1751</v>
+        <v>136.15</v>
       </c>
       <c r="F41" s="4">
-        <v>-4.322168188</v>
+        <v>-3.848870056</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="H41" s="5">
-        <v>1830.1</v>
+        <v>141.6</v>
       </c>
       <c r="I41" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J41" s="43"/>
+      <c r="J41" s="65" t="s">
+        <v>54</v>
+      </c>
       <c r="K41" s="16"/>
       <c r="L41" s="16"/>
       <c r="M41" s="16"/>
@@ -3578,125 +3564,121 @@
       <c r="P41"/>
     </row>
     <row r="42" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="3">
+      <c r="A42" s="42">
+        <v>46300.375694444447</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="5">
+        <v>1</v>
+      </c>
+      <c r="E42" s="5">
+        <v>4510</v>
+      </c>
+      <c r="F42" s="4">
+        <v>-4.0425531909999997</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H42" s="5">
+        <v>4700</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J42" s="17" t="s">
+        <v>117</v>
+      </c>
+      <c r="K42" s="17" t="s">
+        <v>294</v>
+      </c>
+      <c r="L42" s="17">
+        <v>4763</v>
+      </c>
+      <c r="M42" s="17">
+        <f>ABS((D42*E42)-L42)</f>
+        <v>253</v>
+      </c>
+      <c r="N42" s="10" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$636, B42, $C$2:$C$636, C42, $D$2:$D$636, D42, $E$2:$E$636, E42) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" s="61" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="3">
         <v>46252.6875</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B43" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C43" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D42" s="4">
+      <c r="D43" s="4">
         <v>25</v>
       </c>
-      <c r="E42" s="4">
+      <c r="E43" s="4">
         <v>326</v>
       </c>
-      <c r="F42" s="4">
+      <c r="F43" s="4">
         <v>-4.1176470590000003</v>
       </c>
-      <c r="G42" s="2" t="s">
+      <c r="G43" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="H42" s="5">
+      <c r="H43" s="5">
         <v>340</v>
       </c>
-      <c r="I42" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J42" s="65" t="s">
+      <c r="I43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J43" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B42, $C$2:$C$636, C42, $D$2:$D$636, D42, $E$2:$E$636, E42) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O42"/>
-      <c r="P42"/>
-    </row>
-    <row r="43" spans="1:16" s="61" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="42">
-        <v>46300.375694444447</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D43" s="5">
-        <v>1</v>
-      </c>
-      <c r="E43" s="5">
-        <v>4510</v>
-      </c>
-      <c r="F43" s="4">
-        <v>-4.0425531909999997</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="H43" s="5">
-        <v>4700</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J43" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="K43" s="17" t="s">
-        <v>294</v>
-      </c>
-      <c r="L43" s="17">
-        <v>4763</v>
-      </c>
-      <c r="M43" s="17">
-        <f>ABS((D43*E43)-L43)</f>
-        <v>253</v>
-      </c>
-      <c r="N43" s="10" t="str">
+      <c r="K43" s="16"/>
+      <c r="L43" s="16"/>
+      <c r="M43" s="16"/>
+      <c r="N43" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B43, $C$2:$C$636, C43, $D$2:$D$636, D43, $E$2:$E$636, E43) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O43" s="10"/>
-      <c r="P43" s="10"/>
+      <c r="O43"/>
+      <c r="P43"/>
     </row>
     <row r="44" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="3">
-        <v>46252.688194444447</v>
+      <c r="A44" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D44" s="4">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="E44" s="4">
-        <v>136.15</v>
+        <v>1751</v>
       </c>
       <c r="F44" s="4">
-        <v>-3.848870056</v>
+        <v>-4.322168188</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="H44" s="5">
-        <v>141.6</v>
+        <v>1830.1</v>
       </c>
       <c r="I44" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J44" s="65" t="s">
-        <v>54</v>
-      </c>
+      <c r="J44" s="43"/>
       <c r="K44" s="16"/>
       <c r="L44" s="16"/>
       <c r="M44" s="16"/>
@@ -3708,85 +3690,93 @@
       <c r="P44"/>
     </row>
     <row r="45" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C45" s="1" t="s">
+      <c r="A45" s="42">
+        <v>46311.375</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D45" s="4">
-        <v>200</v>
-      </c>
-      <c r="E45" s="4">
-        <v>115.25</v>
+      <c r="D45" s="5">
+        <v>5</v>
+      </c>
+      <c r="E45" s="5">
+        <v>726</v>
       </c>
       <c r="F45" s="4">
-        <v>-3.8140544150000002</v>
+        <v>-4.4736842110000001</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="H45" s="5">
-        <v>119.82</v>
+        <v>760</v>
       </c>
       <c r="I45" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J45" s="43"/>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" t="str">
+      <c r="J45" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="K45" s="17" t="s">
+        <v>331</v>
+      </c>
+      <c r="L45" s="17">
+        <f>5*773</f>
+        <v>3865</v>
+      </c>
+      <c r="M45" s="17">
+        <f>ABS((D45*E45)-L45)</f>
+        <v>235</v>
+      </c>
+      <c r="N45" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B45, $C$2:$C$636, C45, $D$2:$D$636, D45, $E$2:$E$636, E45) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O45"/>
-      <c r="P45"/>
     </row>
     <row r="46" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="42">
-        <v>46301.375694444447</v>
+        <v>46311.595833333333</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D46" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E46" s="5">
-        <v>1664</v>
+        <v>261</v>
       </c>
       <c r="F46" s="4">
-        <v>-3.3681765389999998</v>
+        <v>-5.6057866179999998</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="H46" s="5">
-        <v>1722</v>
+        <v>276.5</v>
       </c>
       <c r="I46" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J46" s="17" t="s">
+      <c r="J46" s="64" t="s">
         <v>40</v>
       </c>
       <c r="K46" s="17" t="s">
-        <v>296</v>
+        <v>333</v>
       </c>
       <c r="L46" s="17">
-        <f>5*1752</f>
-        <v>8760</v>
+        <f>10*283</f>
+        <v>2830</v>
       </c>
       <c r="M46" s="17">
         <f>ABS((D46*E46)-L46)</f>
-        <v>440</v>
+        <v>220</v>
       </c>
       <c r="N46" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B46, $C$2:$C$636, C46, $D$2:$D$636, D46, $E$2:$E$636, E46) &gt; 1, "Duplicate", "Unique")</f>
@@ -3794,240 +3784,237 @@
       </c>
     </row>
     <row r="47" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C47" s="1" t="s">
+      <c r="A47" s="42">
+        <v>46314.375648148147</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D47" s="4">
-        <v>50</v>
-      </c>
-      <c r="E47" s="4">
-        <v>116</v>
+      <c r="D47" s="5">
+        <v>11</v>
+      </c>
+      <c r="E47" s="5">
+        <v>701</v>
       </c>
       <c r="F47" s="4">
-        <v>-3.188115507</v>
+        <v>-5.9060402679999999</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="H47" s="5">
-        <v>119.82</v>
+        <v>745</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J47" s="43"/>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
+      <c r="J47" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="K47" s="17" t="s">
+        <v>346</v>
+      </c>
+      <c r="L47" s="17">
+        <v>8239</v>
+      </c>
+      <c r="M47" s="17">
+        <f>ABS((D47*E47)-L47)</f>
+        <v>528</v>
+      </c>
       <c r="N47" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B47, $C$2:$C$636, C47, $D$2:$D$636, D47, $E$2:$E$636, E47) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O47"/>
-      <c r="P47"/>
     </row>
     <row r="48" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="45">
-        <v>46304.375</v>
-      </c>
-      <c r="B48" s="46" t="s">
-        <v>50</v>
-      </c>
-      <c r="C48" s="46" t="s">
+      <c r="A48" s="42">
+        <v>46295.375</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D48" s="47">
+      <c r="D48" s="5">
+        <v>5</v>
+      </c>
+      <c r="E48" s="5">
+        <v>620</v>
+      </c>
+      <c r="F48" s="4">
+        <v>-6.0819510719999998</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H48" s="5">
+        <v>660.15</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J48" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="K48" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="L48" s="17">
+        <v>3395</v>
+      </c>
+      <c r="M48" s="17">
+        <f>ABS((D48*E48)-L48)</f>
+        <v>295</v>
+      </c>
+      <c r="N48" s="10" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$636, B48, $C$2:$C$636, C48, $D$2:$D$636, D48, $E$2:$E$636, E48) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="3">
+        <v>46121.375</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E48" s="47">
-        <v>852</v>
-      </c>
-      <c r="F48" s="4">
-        <v>-2.3551658930000001</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H48" s="5">
-        <v>872.55</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J48" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="K48" s="25" t="s">
-        <v>310</v>
-      </c>
-      <c r="L48" s="25">
-        <v>8570</v>
-      </c>
-      <c r="M48" s="25">
-        <f>ABS((D48*E48)-L48)</f>
-        <v>50</v>
-      </c>
-      <c r="N48" s="26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B48, $C$2:$C$636, C48, $D$2:$D$636, D48, $E$2:$E$636, E48) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Duplicate</v>
-      </c>
-      <c r="O48" s="27"/>
-      <c r="P48" s="27"/>
-    </row>
-    <row r="49" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="28">
-        <v>46307.375</v>
-      </c>
-      <c r="B49" s="29" t="s">
-        <v>50</v>
-      </c>
-      <c r="C49" s="29" t="s">
+      <c r="D49" s="4">
+        <v>3</v>
+      </c>
+      <c r="E49" s="4">
+        <v>1614</v>
+      </c>
+      <c r="F49" s="4">
+        <v>-6.2717770030000004</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H49" s="5">
+        <v>1722</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J49" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="K49" s="17" t="s">
+        <v>234</v>
+      </c>
+      <c r="L49" s="17">
+        <f>3*1794</f>
+        <v>5382</v>
+      </c>
+      <c r="M49" s="17">
+        <f>ABS((D49*E49)-L49)</f>
+        <v>540</v>
+      </c>
+      <c r="N49" s="10" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$636, B49, $C$2:$C$636, C49, $D$2:$D$636, D49, $E$2:$E$636, E49) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O49"/>
+      <c r="P49"/>
+    </row>
+    <row r="50" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="42">
+        <v>46311.375</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D49" s="30">
+      <c r="D50" s="5">
+        <v>5</v>
+      </c>
+      <c r="E50" s="5">
+        <v>712</v>
+      </c>
+      <c r="F50" s="4">
+        <v>-6.3157894739999998</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H50" s="5">
+        <v>760</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J50" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="K50" s="17" t="s">
+        <v>329</v>
+      </c>
+      <c r="L50" s="17">
+        <v>3810</v>
+      </c>
+      <c r="M50" s="17">
+        <f>ABS((D50*E50)-L50)</f>
+        <v>250</v>
+      </c>
+      <c r="N50" s="10" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$636, B50, $C$2:$C$636, C50, $D$2:$D$636, D50, $E$2:$E$636, E50) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" s="27" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E49" s="30">
-        <v>852</v>
-      </c>
-      <c r="F49" s="4">
-        <v>-2.3551658930000001</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H49" s="5">
-        <v>872.55</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J49" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="K49" s="26" t="s">
-        <v>312</v>
-      </c>
-      <c r="L49" s="26">
-        <v>8670</v>
-      </c>
-      <c r="M49" s="25">
-        <f>ABS((D49*E49)-L49)</f>
-        <v>150</v>
-      </c>
-      <c r="N49" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B49, $C$2:$C$636, C49, $D$2:$D$636, D49, $E$2:$E$636, E49) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Duplicate</v>
-      </c>
-      <c r="O49" s="27"/>
-      <c r="P49" s="27"/>
-    </row>
-    <row r="50" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="45">
-        <v>46308.375</v>
-      </c>
-      <c r="B50" s="46" t="s">
-        <v>50</v>
-      </c>
-      <c r="C50" s="46" t="s">
-        <v>10</v>
-      </c>
-      <c r="D50" s="47">
-        <v>10</v>
-      </c>
-      <c r="E50" s="47">
-        <v>852</v>
-      </c>
-      <c r="F50" s="4">
-        <v>-2.3551658930000001</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H50" s="5">
-        <v>872.55</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J50" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="K50" s="25" t="s">
-        <v>319</v>
-      </c>
-      <c r="L50" s="25">
-        <v>8870</v>
-      </c>
-      <c r="M50" s="25">
-        <f>ABS((D50*E50)-L50)</f>
-        <v>350</v>
-      </c>
-      <c r="N50" s="26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B50, $C$2:$C$636, C50, $D$2:$D$636, D50, $E$2:$E$636, E50) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Duplicate</v>
-      </c>
-      <c r="O50" s="27"/>
-      <c r="P50" s="27"/>
-    </row>
-    <row r="51" spans="1:16" s="27" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="45">
-        <v>46308.375</v>
-      </c>
-      <c r="B51" s="46" t="s">
-        <v>50</v>
-      </c>
-      <c r="C51" s="46" t="s">
-        <v>10</v>
-      </c>
-      <c r="D51" s="47">
-        <v>10</v>
-      </c>
-      <c r="E51" s="47">
-        <v>852</v>
+      <c r="D51" s="4">
+        <v>1</v>
+      </c>
+      <c r="E51" s="4">
+        <v>18552</v>
       </c>
       <c r="F51" s="4">
-        <v>-2.3551658930000001</v>
+        <v>-6.3172246630000002</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="H51" s="5">
-        <v>872.55</v>
+        <v>19803</v>
       </c>
       <c r="I51" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J51" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="K51" s="25" t="s">
-        <v>320</v>
-      </c>
-      <c r="L51" s="25">
-        <v>8770</v>
-      </c>
-      <c r="M51" s="25">
-        <f>ABS((D51*E51)-L51)</f>
-        <v>250</v>
-      </c>
-      <c r="N51" s="26" t="str">
+      <c r="J51" s="65"/>
+      <c r="K51" s="16"/>
+      <c r="L51" s="16"/>
+      <c r="M51" s="16"/>
+      <c r="N51" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B51, $C$2:$C$636, C51, $D$2:$D$636, D51, $E$2:$E$636, E51) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Duplicate</v>
-      </c>
+        <v>Unique</v>
+      </c>
+      <c r="O51"/>
+      <c r="P51"/>
     </row>
     <row r="52" spans="1:16" s="27" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>31</v>
+        <v>99</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>10</v>
@@ -4036,16 +4023,16 @@
         <v>25</v>
       </c>
       <c r="E52" s="4">
-        <v>836</v>
+        <v>251</v>
       </c>
       <c r="F52" s="4">
-        <v>-2.2222222220000001</v>
+        <v>-6.4305684999999997</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="H52" s="5">
-        <v>855</v>
+        <v>268.25</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>8</v>
@@ -4064,46 +4051,45 @@
       <c r="P52"/>
     </row>
     <row r="53" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="42">
-        <v>46311.595833333333</v>
+      <c r="A53" s="62">
+        <v>46309</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>11</v>
+        <v>108</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D53" s="5">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E53" s="5">
-        <v>271</v>
+        <v>4640</v>
       </c>
       <c r="F53" s="4">
-        <v>-1.9891500900000001</v>
+        <v>-6.4327485380000002</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="H53" s="5">
-        <v>276.5</v>
+        <v>4959</v>
       </c>
       <c r="I53" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J53" s="17" t="s">
+      <c r="J53" s="64" t="s">
         <v>40</v>
       </c>
       <c r="K53" s="17" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="L53" s="17">
-        <f>20*283</f>
-        <v>5660</v>
+        <v>4940</v>
       </c>
       <c r="M53" s="17">
         <f>ABS((D53*E53)-L53)</f>
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="N53" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B53, $C$2:$C$636, C53, $D$2:$D$636, D53, $E$2:$E$636, E53) &gt; 1, "Duplicate", "Unique")</f>
@@ -4111,29 +4097,29 @@
       </c>
     </row>
     <row r="54" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="42">
-        <v>46311.375</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C54" s="2" t="s">
+      <c r="A54" s="3">
+        <v>46302.468055555553</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C54" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D54" s="5">
-        <v>5</v>
-      </c>
-      <c r="E54" s="5">
-        <v>746</v>
+      <c r="D54" s="4">
+        <v>2</v>
+      </c>
+      <c r="E54" s="4">
+        <v>3110</v>
       </c>
       <c r="F54" s="4">
-        <v>-1.8421052630000001</v>
+        <v>-6.7745803359999996</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="H54" s="5">
-        <v>760</v>
+        <v>3336</v>
       </c>
       <c r="I54" s="1" t="s">
         <v>8</v>
@@ -4142,15 +4128,15 @@
         <v>40</v>
       </c>
       <c r="K54" s="17" t="s">
-        <v>331</v>
+        <v>298</v>
       </c>
       <c r="L54" s="17">
-        <f>5*773</f>
-        <v>3865</v>
+        <f>2*3334</f>
+        <v>6668</v>
       </c>
       <c r="M54" s="17">
         <f>ABS((D54*E54)-L54)</f>
-        <v>135</v>
+        <v>448</v>
       </c>
       <c r="N54" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B54, $C$2:$C$636, C54, $D$2:$D$636, D54, $E$2:$E$636, E54) &gt; 1, "Duplicate", "Unique")</f>
@@ -4158,82 +4144,75 @@
       </c>
     </row>
     <row r="55" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="42">
-        <v>46310.375</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C55" s="2" t="s">
+      <c r="A55" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D55" s="5">
-        <v>100</v>
-      </c>
-      <c r="E55" s="5">
-        <v>315.10000000000002</v>
+      <c r="D55" s="4">
+        <v>1</v>
+      </c>
+      <c r="E55" s="4">
+        <v>4364</v>
       </c>
       <c r="F55" s="4">
-        <v>-1.7155333749999999</v>
+        <v>-7.1489361699999998</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>44</v>
+        <v>97</v>
       </c>
       <c r="H55" s="5">
-        <v>320.60000000000002</v>
+        <v>4700</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J55" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="K55" s="17" t="s">
-        <v>326</v>
-      </c>
-      <c r="L55" s="17">
-        <v>32200</v>
-      </c>
-      <c r="M55" s="17">
-        <f>ABS((D55*E55)-L55)</f>
-        <v>689.99999999999636</v>
-      </c>
-      <c r="N55" s="10" t="str">
+      <c r="J55" s="66" t="s">
+        <v>40</v>
+      </c>
+      <c r="K55" s="16"/>
+      <c r="L55" s="16"/>
+      <c r="M55" s="16"/>
+      <c r="N55" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B55, $C$2:$C$636, C55, $D$2:$D$636, D55, $E$2:$E$636, E55) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
+      <c r="O55"/>
+      <c r="P55"/>
     </row>
     <row r="56" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D56" s="4">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="E56" s="4">
-        <v>4010</v>
+        <v>111</v>
       </c>
       <c r="F56" s="4">
-        <v>-1.5709376530000001</v>
+        <v>-7.3610415619999996</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H56" s="5">
-        <v>4074</v>
+        <v>119.82</v>
       </c>
       <c r="I56" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J56" s="65" t="s">
-        <v>40</v>
-      </c>
+      <c r="J56" s="65"/>
       <c r="K56" s="16"/>
       <c r="L56" s="16"/>
       <c r="M56" s="16"/>
@@ -4241,13 +4220,15 @@
         <f>IF(COUNTIFS( $B$2:$B$636, B56, $C$2:$C$636, C56, $D$2:$D$636, D56, $E$2:$E$636, E56) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
+      <c r="O56"/>
+      <c r="P56"/>
     </row>
     <row r="57" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="3">
-        <v>46307.375</v>
+        <v>46286.375</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>10</v>
@@ -4256,32 +4237,33 @@
         <v>5</v>
       </c>
       <c r="E57" s="4">
-        <v>3288</v>
+        <v>702</v>
       </c>
       <c r="F57" s="4">
-        <v>-1.4388489209999999</v>
+        <v>-7.6315789470000004</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="H57" s="5">
-        <v>3336</v>
+        <v>760</v>
       </c>
       <c r="I57" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J57" s="71" t="s">
-        <v>54</v>
-      </c>
-      <c r="K57" t="s">
-        <v>313</v>
-      </c>
-      <c r="L57">
-        <v>16740</v>
+      <c r="J57" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="K57" s="17" t="s">
+        <v>276</v>
+      </c>
+      <c r="L57" s="17">
+        <f>7470/2</f>
+        <v>3735</v>
       </c>
       <c r="M57" s="17">
         <f>ABS((D57*E57)-L57)</f>
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="N57" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B57, $C$2:$C$636, C57, $D$2:$D$636, D57, $E$2:$E$636, E57) &gt; 1, "Duplicate", "Unique")</f>
@@ -4289,132 +4271,130 @@
       </c>
     </row>
     <row r="58" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="42">
-        <v>46301.393055555556</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C58" s="2" t="s">
+      <c r="A58" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C58" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D58" s="5">
+      <c r="D58" s="4">
         <v>1</v>
       </c>
-      <c r="E58" s="5">
-        <v>19550</v>
+      <c r="E58" s="4">
+        <v>4560</v>
       </c>
       <c r="F58" s="4">
-        <v>-1.2775842040000001</v>
+        <v>-8.0459770109999997</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="H58" s="5">
-        <v>19803</v>
+        <v>4959</v>
       </c>
       <c r="I58" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J58" s="64" t="s">
-        <v>40</v>
-      </c>
-      <c r="K58" s="17" t="s">
-        <v>297</v>
-      </c>
-      <c r="L58" s="17">
-        <v>20020</v>
-      </c>
-      <c r="M58" s="17">
-        <f>ABS((D58*E58)-L58)</f>
-        <v>470</v>
-      </c>
-      <c r="N58" s="10" t="str">
+      <c r="J58" s="65"/>
+      <c r="K58" s="16"/>
+      <c r="L58" s="16"/>
+      <c r="M58" s="16"/>
+      <c r="N58" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B58, $C$2:$C$636, C58, $D$2:$D$636, D58, $E$2:$E$636, E58) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="59" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="59" t="s">
-        <v>61</v>
-      </c>
-      <c r="B59" s="50" t="s">
-        <v>50</v>
-      </c>
-      <c r="C59" s="50" t="s">
+      <c r="O58"/>
+      <c r="P58"/>
+    </row>
+    <row r="59" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="42">
+        <v>46310.40347222222</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D59" s="51">
-        <v>40</v>
-      </c>
-      <c r="E59" s="51">
-        <v>862</v>
+      <c r="D59" s="5">
+        <v>300</v>
+      </c>
+      <c r="E59" s="5">
+        <v>32.01</v>
       </c>
       <c r="F59" s="4">
-        <v>-1.2090997649999999</v>
+        <v>-8.3333333330000006</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H59" s="5">
-        <v>872.55</v>
+        <v>34.92</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J59" s="68" t="s">
+      <c r="J59" s="64" t="s">
         <v>54</v>
       </c>
-      <c r="K59" s="60"/>
-      <c r="L59" s="60"/>
-      <c r="M59" s="60"/>
-      <c r="N59" s="52" t="str">
+      <c r="K59" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="L59" s="17">
+        <v>10263</v>
+      </c>
+      <c r="M59" s="17">
+        <f>ABS((D59*E59)-L59)</f>
+        <v>660</v>
+      </c>
+      <c r="N59" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B59, $C$2:$C$636, C59, $D$2:$D$636, D59, $E$2:$E$636, E59) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O59" s="52"/>
-      <c r="P59" s="52"/>
     </row>
     <row r="60" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A60" s="42">
         <v>46314.37537037037</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D60" s="5">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E60" s="5">
-        <v>336</v>
+        <v>680</v>
       </c>
       <c r="F60" s="4">
-        <v>-1.1764705879999999</v>
+        <v>-8.7248322149999993</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H60" s="5">
-        <v>340</v>
+        <v>745</v>
       </c>
       <c r="I60" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J60" s="17" t="s">
-        <v>54</v>
+      <c r="J60" s="64" t="s">
+        <v>40</v>
       </c>
       <c r="K60" s="17" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="L60" s="17">
-        <v>8700</v>
+        <v>3650</v>
       </c>
       <c r="M60" s="17">
         <f>ABS((D60*E60)-L60)</f>
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="N60" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B60, $C$2:$C$636, C60, $D$2:$D$636, D60, $E$2:$E$636, E60) &gt; 1, "Duplicate", "Unique")</f>
@@ -4422,128 +4402,119 @@
       </c>
     </row>
     <row r="61" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="42">
-        <v>46308.620138888888</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C61" s="2" t="s">
+      <c r="A61" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D61" s="5">
-        <v>10</v>
-      </c>
-      <c r="E61" s="5">
-        <v>3310</v>
+      <c r="D61" s="4">
+        <v>1</v>
+      </c>
+      <c r="E61" s="4">
+        <v>18052</v>
       </c>
       <c r="F61" s="4">
-        <v>-0.77937649880000004</v>
+        <v>-8.8420946320000002</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H61" s="5">
-        <v>3336</v>
+        <v>19803</v>
       </c>
       <c r="I61" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J61" s="64" t="s">
-        <v>54</v>
-      </c>
-      <c r="K61" s="17" t="s">
-        <v>315</v>
-      </c>
-      <c r="L61" s="17">
-        <v>33800</v>
-      </c>
-      <c r="M61" s="17">
-        <f>ABS((D61*E61)-L61)</f>
-        <v>700</v>
-      </c>
+      <c r="J61" s="65"/>
+      <c r="K61" s="16"/>
+      <c r="L61" s="16"/>
+      <c r="M61" s="16"/>
       <c r="N61" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B61, $C$2:$C$636, C61, $D$2:$D$636, D61, $E$2:$E$636, E61) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
+      <c r="O61"/>
+      <c r="P61"/>
     </row>
     <row r="62" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A62" s="42">
-        <v>46304.375</v>
+        <v>46289.375</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>10</v>
       </c>
       <c r="D62" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E62" s="5">
-        <v>1708.7</v>
+        <v>601</v>
       </c>
       <c r="F62" s="4">
-        <v>-0.77235772359999999</v>
+        <v>-8.9600848289999995</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="H62" s="5">
-        <v>1722</v>
+        <v>660.15</v>
       </c>
       <c r="I62" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J62" s="17" t="s">
-        <v>54</v>
+      <c r="J62" s="64" t="s">
+        <v>40</v>
       </c>
       <c r="K62" s="17" t="s">
-        <v>309</v>
+        <v>280</v>
       </c>
       <c r="L62" s="17">
-        <v>17487</v>
+        <v>3245</v>
       </c>
       <c r="M62" s="17">
         <f>ABS((D62*E62)-L62)</f>
-        <v>400</v>
-      </c>
-      <c r="N62" t="str">
+        <v>240</v>
+      </c>
+      <c r="N62" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B62, $C$2:$C$636, C62, $D$2:$D$636, D62, $E$2:$E$636, E62) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
     <row r="63" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="6" t="s">
-        <v>61</v>
+      <c r="A63" s="3">
+        <v>46252.635416666664</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D63" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E63" s="4">
-        <v>1614</v>
+        <v>2892</v>
       </c>
       <c r="F63" s="4">
-        <v>-0.71968997970000004</v>
+        <v>-9.1851154029999993</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="H63" s="5">
-        <v>1625.7</v>
+        <v>3184.5</v>
       </c>
       <c r="I63" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J63" s="67" t="s">
-        <v>40</v>
-      </c>
+      <c r="J63" s="65"/>
       <c r="K63" s="16"/>
       <c r="L63" s="16"/>
       <c r="M63" s="16"/>
@@ -4555,74 +4526,80 @@
       <c r="P63"/>
     </row>
     <row r="64" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="42">
+        <v>46303.375</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D64" s="5">
+        <v>2</v>
+      </c>
+      <c r="E64" s="5">
+        <v>1294</v>
+      </c>
+      <c r="F64" s="4">
+        <v>-9.9199443089999999</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="H64" s="5">
+        <v>1436.5</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J64" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="K64" s="17" t="s">
+        <v>301</v>
+      </c>
+      <c r="L64" s="17">
+        <v>2852</v>
+      </c>
+      <c r="M64" s="17">
+        <f>ABS((D64*E64)-L64)</f>
+        <v>264</v>
+      </c>
+      <c r="N64" s="10" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$636, B64, $C$2:$C$636, C64, $D$2:$D$636, D64, $E$2:$E$636, E64) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D64" s="4">
-        <v>50</v>
-      </c>
-      <c r="E64" s="4">
-        <v>119</v>
-      </c>
-      <c r="F64" s="4">
-        <v>-0.68435987310000002</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H64" s="5">
-        <v>119.82</v>
-      </c>
-      <c r="I64" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J64" s="65"/>
-      <c r="K64" s="16"/>
-      <c r="L64" s="16"/>
-      <c r="M64" s="16"/>
-      <c r="N64" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B64, $C$2:$C$636, C64, $D$2:$D$636, D64, $E$2:$E$636, E64) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="O64"/>
-    </row>
-    <row r="65" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="3">
-        <v>46252.635416666664</v>
-      </c>
       <c r="B65" s="1" t="s">
-        <v>31</v>
+        <v>108</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D65" s="4">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="E65" s="4">
-        <v>850</v>
+        <v>4456</v>
       </c>
       <c r="F65" s="4">
-        <v>-0.58479532160000003</v>
+        <v>-10.143174030000001</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="H65" s="5">
-        <v>855</v>
+        <v>4959</v>
       </c>
       <c r="I65" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J65" s="66" t="s">
-        <v>54</v>
-      </c>
+      <c r="J65" s="65"/>
       <c r="K65" s="16"/>
       <c r="L65" s="16"/>
       <c r="M65" s="16"/>
@@ -4630,91 +4607,95 @@
         <f>IF(COUNTIFS( $B$2:$B$636, B65, $C$2:$C$636, C65, $D$2:$D$636, D65, $E$2:$E$636, E65) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
+      <c r="O65"/>
       <c r="P65"/>
     </row>
-    <row r="66" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C66" s="1" t="s">
+    <row r="66" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="42">
+        <v>46308.536805555559</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C66" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D66" s="4">
-        <v>69</v>
-      </c>
-      <c r="E66" s="4">
-        <v>1277</v>
+      <c r="D66" s="5">
+        <v>200</v>
+      </c>
+      <c r="E66" s="5">
+        <v>31.1</v>
       </c>
       <c r="F66" s="4">
-        <v>0.55118110239999996</v>
+        <v>-10.93928981</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="H66" s="5">
-        <v>1270</v>
+        <v>34.92</v>
       </c>
       <c r="I66" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J66" s="65"/>
-      <c r="K66" s="16"/>
-      <c r="L66" s="16"/>
-      <c r="M66" s="16"/>
+      <c r="J66" s="64" t="s">
+        <v>54</v>
+      </c>
+      <c r="K66" s="17" t="s">
+        <v>318</v>
+      </c>
+      <c r="L66" s="17">
+        <v>6580</v>
+      </c>
+      <c r="M66" s="17">
+        <f>ABS((D66*E66)-L66)</f>
+        <v>360</v>
+      </c>
       <c r="N66" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B66, $C$2:$C$636, C66, $D$2:$D$636, D66, $E$2:$E$636, E66) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O66"/>
-      <c r="P66"/>
     </row>
     <row r="67" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="3">
-        <v>46254.375</v>
+      <c r="A67" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>32</v>
+        <v>108</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D67" s="4">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E67" s="4">
-        <v>2230</v>
+        <v>4415</v>
       </c>
       <c r="F67" s="4">
-        <v>0.8958465297</v>
+        <v>-10.96995362</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="H67" s="5">
-        <v>2210.1999999999998</v>
+        <v>4959</v>
       </c>
       <c r="I67" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J67" s="69" t="s">
-        <v>54</v>
-      </c>
-      <c r="K67" s="16" t="s">
-        <v>146</v>
-      </c>
+      <c r="J67" s="65"/>
+      <c r="K67" s="16"/>
       <c r="L67" s="16"/>
       <c r="M67" s="16"/>
-      <c r="N67" s="10" t="str">
+      <c r="N67" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B67, $C$2:$C$636, C67, $D$2:$D$636, D67, $E$2:$E$636, E67) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="O67"/>
       <c r="P67"/>
     </row>
-    <row r="68" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A68" s="42">
         <v>46314.375659722224</v>
       </c>
@@ -4761,92 +4742,84 @@
       </c>
     </row>
     <row r="69" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="3">
-        <v>46261.375</v>
+      <c r="A69" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D69" s="4">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E69" s="4">
-        <v>870</v>
+        <v>4164</v>
       </c>
       <c r="F69" s="4">
-        <v>1.754385965</v>
+        <v>-11.404255320000001</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="H69" s="5">
-        <v>855</v>
+        <v>4700</v>
       </c>
       <c r="I69" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J69" s="64" t="s">
+      <c r="J69" s="65"/>
+      <c r="K69" s="16"/>
+      <c r="L69" s="16"/>
+      <c r="M69" s="16"/>
+      <c r="N69" t="str">
+        <f>IF(COUNTIFS( $B$2:$B$636, B69, $C$2:$C$636, C69, $D$2:$D$636, D69, $E$2:$E$636, E69) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+      <c r="O69"/>
+      <c r="P69"/>
+    </row>
+    <row r="70" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="42">
+        <v>46311.375</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D70" s="5">
+        <v>5</v>
+      </c>
+      <c r="E70" s="5">
+        <v>660</v>
+      </c>
+      <c r="F70" s="4">
+        <v>-11.40939597</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H70" s="5">
+        <v>745</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J70" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="K69" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="L69" s="17">
-        <v>17700</v>
-      </c>
-      <c r="M69" s="17">
-        <f>ABS((D69*E69)-L69)</f>
-        <v>300</v>
-      </c>
-      <c r="N69" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B69, $C$2:$C$636, C69, $D$2:$D$636, D69, $E$2:$E$636, E69) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-      <c r="P69" s="22"/>
-    </row>
-    <row r="70" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="3">
-        <v>46283.375</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D70" s="4">
-        <v>20</v>
-      </c>
-      <c r="E70" s="4">
-        <v>870.2</v>
-      </c>
-      <c r="F70" s="4">
-        <v>1.7777777779999999</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H70" s="5">
-        <v>855</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J70" s="64" t="s">
-        <v>54</v>
-      </c>
       <c r="K70" s="17" t="s">
-        <v>274</v>
+        <v>328</v>
       </c>
       <c r="L70" s="17">
-        <v>17920</v>
+        <v>3550</v>
       </c>
       <c r="M70" s="17">
         <f>ABS((D70*E70)-L70)</f>
-        <v>516</v>
+        <v>250</v>
       </c>
       <c r="N70" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B70, $C$2:$C$636, C70, $D$2:$D$636, D70, $E$2:$E$636, E70) &gt; 1, "Duplicate", "Unique")</f>
@@ -4854,34 +4827,34 @@
       </c>
     </row>
     <row r="71" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="3">
-        <v>46252.6875</v>
+      <c r="A71" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D71" s="4">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="E71" s="4">
-        <v>122</v>
+        <v>701</v>
       </c>
       <c r="F71" s="4">
-        <v>1.8193957599999999</v>
+        <v>-11.71284635</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="H71" s="5">
-        <v>119.82</v>
+        <v>794</v>
       </c>
       <c r="I71" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J71" s="66" t="s">
+      <c r="J71" s="65" t="s">
         <v>40</v>
       </c>
       <c r="K71" s="16"/>
@@ -4891,8 +4864,10 @@
         <f>IF(COUNTIFS( $B$2:$B$636, B71, $C$2:$C$636, C71, $D$2:$D$636, D71, $E$2:$E$636, E71) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="72" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O71"/>
+      <c r="P71"/>
+    </row>
+    <row r="72" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A72" s="42">
         <v>46314.375659722224</v>
       </c>
@@ -4939,48 +4914,53 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="73" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A73" s="3">
-        <v>46252.635416666664</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C73" s="1" t="s">
+    <row r="73" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="42">
+        <v>46308.578472222223</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C73" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D73" s="4">
-        <v>3</v>
-      </c>
-      <c r="E73" s="4">
-        <v>1302</v>
+      <c r="D73" s="5">
+        <v>13</v>
+      </c>
+      <c r="E73" s="5">
+        <v>1209</v>
       </c>
       <c r="F73" s="4">
-        <v>2.5196850390000001</v>
+        <v>-12.38495543</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>78</v>
+        <v>321</v>
       </c>
       <c r="H73" s="5">
-        <v>1270</v>
+        <v>1379.9</v>
       </c>
       <c r="I73" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J73" s="65" t="s">
-        <v>40</v>
-      </c>
-      <c r="K73" s="16"/>
-      <c r="L73" s="16"/>
-      <c r="M73" s="16"/>
+      <c r="J73" s="64" t="s">
+        <v>54</v>
+      </c>
+      <c r="K73" s="17" t="s">
+        <v>316</v>
+      </c>
+      <c r="L73" s="17">
+        <v>17017</v>
+      </c>
+      <c r="M73" s="17">
+        <f>ABS((D73*E73)-L73)</f>
+        <v>1300</v>
+      </c>
       <c r="N73" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B73, $C$2:$C$636, C73, $D$2:$D$636, D73, $E$2:$E$636, E73) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O73"/>
-      <c r="P73"/>
-    </row>
-    <row r="74" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="74" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="42">
         <v>46293.401388888888</v>
       </c>
@@ -5026,7 +5006,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="75" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A75" s="42">
         <v>46314.375659722224</v>
       </c>
@@ -5072,7 +5052,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="76" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A76" s="3">
         <v>46307.617361111108</v>
       </c>
@@ -5118,7 +5098,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="77" spans="1:16" s="27" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:16" s="27" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A77" s="42">
         <v>46314.375659722224</v>
       </c>
@@ -5167,7 +5147,7 @@
       <c r="O77" s="10"/>
       <c r="P77" s="10"/>
     </row>
-    <row r="78" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="42">
         <v>46314.375659722224</v>
       </c>
@@ -5213,7 +5193,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="79" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A79" s="42">
         <v>46304.375</v>
       </c>
@@ -5259,7 +5239,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="80" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A80" s="8" t="s">
         <v>61</v>
       </c>
@@ -5295,7 +5275,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="81" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A81" s="42">
         <v>46293.375694444447</v>
       </c>
@@ -5342,38 +5322,47 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="82" spans="1:16" s="27" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A82" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C82" s="1" t="s">
+    <row r="82" spans="1:16" s="27" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="42">
+        <v>46308.538888888892</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D82" s="4">
-        <v>3</v>
-      </c>
-      <c r="E82" s="4">
-        <v>3810</v>
+      <c r="D82" s="5">
+        <v>8</v>
+      </c>
+      <c r="E82" s="5">
+        <v>2155</v>
       </c>
       <c r="F82" s="4">
-        <v>4.0443485619999997</v>
+        <v>-12.430411640000001</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H82" s="5">
-        <v>3661.9</v>
+        <v>2460.9</v>
       </c>
       <c r="I82" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J82" s="65"/>
-      <c r="K82" s="16"/>
-      <c r="L82" s="16"/>
-      <c r="M82" s="16"/>
+      <c r="J82" s="64" t="s">
+        <v>54</v>
+      </c>
+      <c r="K82" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="L82" s="17">
+        <v>18040</v>
+      </c>
+      <c r="M82" s="17">
+        <f>ABS((D82*E82)-L82)</f>
+        <v>800</v>
+      </c>
       <c r="N82" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B82, $C$2:$C$636, C82, $D$2:$D$636, D82, $E$2:$E$636, E82) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
@@ -5430,7 +5419,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="84" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="42">
         <v>46314.40357638889</v>
       </c>
@@ -5476,48 +5465,53 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="85" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B85" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C85" s="1" t="s">
+    <row r="85" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="42">
+        <v>46304.387499999997</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C85" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D85" s="4">
-        <v>50</v>
-      </c>
-      <c r="E85" s="4">
-        <v>206</v>
+      <c r="D85" s="5">
+        <v>500</v>
+      </c>
+      <c r="E85" s="5">
+        <v>30.3</v>
       </c>
       <c r="F85" s="4">
-        <v>4.3354943270000001</v>
+        <v>-13.23024055</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="H85" s="5">
-        <v>197.44</v>
+        <v>34.92</v>
       </c>
       <c r="I85" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J85" s="65" t="s">
-        <v>40</v>
-      </c>
-      <c r="K85" s="16"/>
-      <c r="L85" s="16"/>
-      <c r="M85" s="16"/>
+      <c r="J85" s="64" t="s">
+        <v>54</v>
+      </c>
+      <c r="K85" s="17" t="s">
+        <v>304</v>
+      </c>
+      <c r="L85" s="17">
+        <v>15850</v>
+      </c>
+      <c r="M85" s="17">
+        <f>ABS((D85*E85)-L85)</f>
+        <v>700</v>
+      </c>
       <c r="N85" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B85, $C$2:$C$636, C85, $D$2:$D$636, D85, $E$2:$E$636, E85) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O85"/>
-      <c r="P85"/>
-    </row>
-    <row r="86" spans="1:16" s="23" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="86" spans="1:16" s="23" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -5563,30 +5557,32 @@
         <v>61</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D87" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E87" s="4">
-        <v>3830</v>
+        <v>2752</v>
       </c>
       <c r="F87" s="4">
-        <v>4.5905131219999999</v>
+        <v>-13.581409949999999</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="H87" s="5">
-        <v>3661.9</v>
+        <v>3184.5</v>
       </c>
       <c r="I87" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J87" s="65"/>
+      <c r="J87" s="65" t="s">
+        <v>40</v>
+      </c>
       <c r="K87" s="16"/>
       <c r="L87" s="16"/>
       <c r="M87" s="16"/>
@@ -5594,8 +5590,10 @@
         <f>IF(COUNTIFS( $B$2:$B$636, B87, $C$2:$C$636, C87, $D$2:$D$636, D87, $E$2:$E$636, E87) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="88" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O87"/>
+      <c r="P87"/>
+    </row>
+    <row r="88" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A88" s="42">
         <v>46314.375659722224</v>
       </c>
@@ -5641,7 +5639,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="89" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A89" s="42">
         <v>46314.37568287037</v>
       </c>
@@ -5737,7 +5735,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="91" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="3">
         <v>46276.375</v>
       </c>
@@ -5784,42 +5782,51 @@
       </c>
     </row>
     <row r="92" spans="1:16" s="22" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C92" s="1" t="s">
+      <c r="A92" s="42">
+        <v>46311.375</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D92" s="4">
-        <v>2</v>
-      </c>
-      <c r="E92" s="4">
-        <v>3856</v>
+      <c r="D92" s="5">
+        <v>5</v>
+      </c>
+      <c r="E92" s="5">
+        <v>640</v>
       </c>
       <c r="F92" s="4">
-        <v>5.3005270490000003</v>
+        <v>-14.09395973</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="H92" s="5">
-        <v>3661.9</v>
+        <v>745</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J92" s="65"/>
-      <c r="K92" s="16"/>
-      <c r="L92" s="16"/>
-      <c r="M92" s="16"/>
-      <c r="N92" t="str">
+      <c r="J92" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="K92" s="17" t="s">
+        <v>330</v>
+      </c>
+      <c r="L92" s="17">
+        <v>3450</v>
+      </c>
+      <c r="M92" s="17">
+        <f>ABS((D92*E92)-L92)</f>
+        <v>250</v>
+      </c>
+      <c r="N92" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B92, $C$2:$C$636, C92, $D$2:$D$636, D92, $E$2:$E$636, E92) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O92" s="18"/>
+      <c r="O92" s="10"/>
       <c r="P92" s="10"/>
     </row>
     <row r="93" spans="1:16" s="27" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -5872,7 +5879,7 @@
       </c>
       <c r="P93" s="10"/>
     </row>
-    <row r="94" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A94" s="3">
         <v>46267.461111111108</v>
       </c>
@@ -5920,7 +5927,7 @@
       <c r="O94" s="10"/>
       <c r="P94" s="10"/>
     </row>
-    <row r="95" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A95" s="45">
         <v>46296.586111111108</v>
       </c>
@@ -5968,7 +5975,7 @@
       <c r="O95" s="27"/>
       <c r="P95" s="27"/>
     </row>
-    <row r="96" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="45">
         <v>46296.420138888891</v>
       </c>
@@ -6016,7 +6023,7 @@
       <c r="O96" s="27"/>
       <c r="P96" s="27"/>
     </row>
-    <row r="97" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A97" s="42">
         <v>46310.394444444442</v>
       </c>
@@ -6062,45 +6069,53 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="98" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B98" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C98" s="1" t="s">
+    <row r="98" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="42">
+        <v>46304.388888888891</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D98" s="4">
-        <v>5</v>
-      </c>
-      <c r="E98" s="4">
-        <v>3888</v>
+      <c r="D98" s="5">
+        <v>9</v>
+      </c>
+      <c r="E98" s="5">
+        <v>2105</v>
       </c>
       <c r="F98" s="4">
-        <v>6.1743903439999999</v>
+        <v>-14.46218863</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H98" s="5">
-        <v>3661.9</v>
+        <v>2460.9</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J98" s="65"/>
-      <c r="K98" s="16"/>
-      <c r="L98" s="16"/>
-      <c r="M98" s="16"/>
+      <c r="J98" s="64" t="s">
+        <v>54</v>
+      </c>
+      <c r="K98" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="L98" s="17">
+        <v>19395</v>
+      </c>
+      <c r="M98" s="17">
+        <f>ABS((D98*E98)-L98)</f>
+        <v>450</v>
+      </c>
       <c r="N98" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B98, $C$2:$C$636, C98, $D$2:$D$636, D98, $E$2:$E$636, E98) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="O98" s="23"/>
-    </row>
-    <row r="99" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="99" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A99" s="3">
         <v>46286.375694444447</v>
       </c>
@@ -6149,44 +6164,46 @@
     </row>
     <row r="100" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="3">
-        <v>46252.645138888889</v>
+        <v>46031.4375</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>67</v>
+        <v>204</v>
       </c>
       <c r="C100" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D100" s="4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E100" s="4">
-        <v>401</v>
+        <v>1052</v>
       </c>
       <c r="F100" s="4">
-        <v>6.3096500530000004</v>
+        <v>-14.464590619999999</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>68</v>
+        <v>215</v>
       </c>
       <c r="H100" s="5">
-        <v>377.2</v>
+        <v>1229.9000000000001</v>
       </c>
       <c r="I100" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J100" s="70" t="s">
+      <c r="J100" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="K100" s="16"/>
-      <c r="L100" s="16"/>
-      <c r="M100" s="16"/>
-      <c r="N100" t="str">
+      <c r="M100" s="17">
+        <f>ABS((D100*E100)-L100)</f>
+        <v>3156</v>
+      </c>
+      <c r="N100" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B100, $C$2:$C$636, C100, $D$2:$D$636, D100, $E$2:$E$636, E100) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="101" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="P100" s="18"/>
+    </row>
+    <row r="101" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="3">
         <v>46267.375</v>
       </c>
@@ -6232,7 +6249,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="102" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="11">
         <v>46243.375</v>
       </c>
@@ -6279,7 +6296,7 @@
       </c>
       <c r="P102"/>
     </row>
-    <row r="103" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="3">
         <v>46262.375</v>
       </c>
@@ -6325,7 +6342,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="104" spans="1:16" s="27" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:16" s="27" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="11">
         <v>46243.375</v>
       </c>
@@ -6423,7 +6440,7 @@
       </c>
       <c r="P105" s="10"/>
     </row>
-    <row r="106" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A106" s="3">
         <v>46267.38958333333</v>
       </c>
@@ -6474,32 +6491,30 @@
         <v>61</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C107" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D107" s="4">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="E107" s="4">
-        <v>212</v>
+        <v>4014</v>
       </c>
       <c r="F107" s="4">
-        <v>7.3743922199999998</v>
+        <v>-14.595744679999999</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="H107" s="5">
-        <v>197.44</v>
+        <v>4700</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J107" s="65" t="s">
-        <v>40</v>
-      </c>
+      <c r="J107" s="65"/>
       <c r="K107" s="16"/>
       <c r="L107" s="16"/>
       <c r="M107" s="16"/>
@@ -6507,8 +6522,10 @@
         <f>IF(COUNTIFS( $B$2:$B$636, B107, $C$2:$C$636, C107, $D$2:$D$636, D107, $E$2:$E$636, E107) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="108" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O107"/>
+      <c r="P107"/>
+    </row>
+    <row r="108" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="11">
         <v>46273.375</v>
       </c>
@@ -6652,7 +6669,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="111" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A111" s="62">
         <v>46309</v>
       </c>
@@ -6699,52 +6716,45 @@
       </c>
     </row>
     <row r="112" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="3">
-        <v>46268.385416666664</v>
+      <c r="A112" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D112" s="4">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="E112" s="4">
-        <v>214</v>
+        <v>2660</v>
       </c>
       <c r="F112" s="4">
-        <v>8.3873581850000001</v>
+        <v>-16.470403520000001</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="H112" s="5">
-        <v>197.44</v>
+        <v>3184.5</v>
       </c>
       <c r="I112" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J112" s="64" t="s">
-        <v>54</v>
-      </c>
-      <c r="K112" s="17" t="s">
-        <v>229</v>
-      </c>
-      <c r="L112" s="17">
-        <v>21900</v>
-      </c>
-      <c r="M112" s="17">
-        <f>ABS((D112*E112)-L112)</f>
-        <v>500</v>
-      </c>
-      <c r="N112" s="10" t="str">
+      <c r="J112" s="65"/>
+      <c r="K112" s="16"/>
+      <c r="L112" s="16"/>
+      <c r="M112" s="16"/>
+      <c r="N112" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B112, $C$2:$C$636, C112, $D$2:$D$636, D112, $E$2:$E$636, E112) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="113" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O112"/>
+      <c r="P112"/>
+    </row>
+    <row r="113" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A113" s="3">
         <v>46280.435416666667</v>
       </c>
@@ -6790,7 +6800,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="114" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A114" s="11">
         <v>46243.375</v>
       </c>
@@ -6837,7 +6847,7 @@
       </c>
       <c r="P114"/>
     </row>
-    <row r="115" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A115" s="11">
         <v>46273.375</v>
       </c>
@@ -6883,7 +6893,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="116" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A116" s="3">
         <v>46266.642361111109</v>
       </c>
@@ -6931,7 +6941,7 @@
       <c r="O116" s="10"/>
       <c r="P116" s="10"/>
     </row>
-    <row r="117" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="3">
         <v>46261.375</v>
       </c>
@@ -6977,7 +6987,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="118" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="3">
         <v>46266.375</v>
       </c>
@@ -7024,7 +7034,7 @@
       </c>
       <c r="P118" s="27"/>
     </row>
-    <row r="119" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A119" s="8" t="s">
         <v>61</v>
       </c>
@@ -7107,7 +7117,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="121" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A121" s="3">
         <v>46274.375</v>
       </c>
@@ -7155,7 +7165,7 @@
       <c r="O121" s="10"/>
       <c r="P121" s="10"/>
     </row>
-    <row r="122" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="3">
         <v>46269.411111111112</v>
       </c>
@@ -7201,7 +7211,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="123" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A123" s="3">
         <v>46267.375</v>
       </c>
@@ -7248,7 +7258,7 @@
       </c>
       <c r="P123" s="18"/>
     </row>
-    <row r="124" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A124" s="11">
         <v>46252.6875</v>
       </c>
@@ -7284,7 +7294,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="125" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A125" s="28">
         <v>46272.451388888891</v>
       </c>
@@ -7332,7 +7342,7 @@
       <c r="O125" s="27"/>
       <c r="P125" s="27"/>
     </row>
-    <row r="126" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="28">
         <v>46272.390972222223</v>
       </c>
@@ -7380,7 +7390,7 @@
       <c r="O126" s="27"/>
       <c r="P126" s="27"/>
     </row>
-    <row r="127" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A127" s="3">
         <v>46262.375</v>
       </c>
@@ -7427,7 +7437,7 @@
       </c>
       <c r="O127" s="27"/>
     </row>
-    <row r="128" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A128" s="3">
         <v>46294.375</v>
       </c>
@@ -7522,7 +7532,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="130" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="11">
         <v>46253.375</v>
       </c>
@@ -7610,7 +7620,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="132" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A132" s="42">
         <v>46314.375659722224</v>
       </c>
@@ -7799,7 +7809,7 @@
       </c>
       <c r="P135"/>
     </row>
-    <row r="136" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A136" s="42">
         <v>46304.375</v>
       </c>
@@ -7845,7 +7855,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="137" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A137" s="3">
         <v>46266.509722222225</v>
       </c>
@@ -7891,7 +7901,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="138" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A138" s="11">
         <v>46252.6875</v>
       </c>
@@ -7927,7 +7937,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="139" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A139" s="3">
         <v>46301.375</v>
       </c>
@@ -7974,7 +7984,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="140" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="3">
         <v>46261.375</v>
       </c>
@@ -8022,7 +8032,7 @@
       <c r="O140" s="10"/>
       <c r="P140" s="10"/>
     </row>
-    <row r="141" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A141" s="3">
         <v>46280.435416666667</v>
       </c>
@@ -8068,7 +8078,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="142" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A142" s="42">
         <v>46303.375</v>
       </c>
@@ -8114,7 +8124,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="143" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A143" s="8" t="s">
         <v>61</v>
       </c>
@@ -8150,7 +8160,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="144" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A144" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -8185,7 +8195,7 @@
       </c>
       <c r="O144" s="27"/>
     </row>
-    <row r="145" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A145" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -8220,7 +8230,7 @@
       </c>
       <c r="P145" s="27"/>
     </row>
-    <row r="146" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A146" s="3">
         <v>46261.375</v>
       </c>
@@ -8267,7 +8277,7 @@
       </c>
       <c r="O146" s="27"/>
     </row>
-    <row r="147" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A147" s="28">
         <v>46265.375694444447</v>
       </c>
@@ -8313,7 +8323,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="148" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A148" s="28">
         <v>46266.375694444447</v>
       </c>
@@ -8361,7 +8371,7 @@
       <c r="O148" s="10"/>
       <c r="P148" s="10"/>
     </row>
-    <row r="149" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="28">
         <v>46267.424305555556</v>
       </c>
@@ -8409,7 +8419,7 @@
       <c r="O149" s="27"/>
       <c r="P149" s="27"/>
     </row>
-    <row r="150" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="3">
         <v>46260.425694444442</v>
       </c>
@@ -8456,7 +8466,7 @@
       </c>
       <c r="P150" s="27"/>
     </row>
-    <row r="151" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A151" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -8503,7 +8513,7 @@
       </c>
       <c r="P151"/>
     </row>
-    <row r="152" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A152" s="8" t="s">
         <v>61</v>
       </c>
@@ -8539,7 +8549,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="153" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A153" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -8573,7 +8583,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="154" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" s="3">
         <v>46261.375694444447</v>
       </c>
@@ -8669,50 +8679,45 @@
       </c>
     </row>
     <row r="156" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A156" s="3">
-        <v>46261.375</v>
+      <c r="A156" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D156" s="4">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="E156" s="4">
-        <v>204</v>
+        <v>2560</v>
       </c>
       <c r="F156" s="4">
-        <v>12.27297744</v>
+        <v>-19.610613910000001</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>69</v>
+        <v>92</v>
       </c>
       <c r="H156" s="5">
-        <v>181.7</v>
+        <v>3184.5</v>
       </c>
       <c r="I156" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J156" s="64" t="s">
+      <c r="J156" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="K156" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="L156" s="17">
-        <v>10550</v>
-      </c>
-      <c r="M156" s="17">
-        <f>ABS((D156*E156)-L156)</f>
-        <v>350</v>
-      </c>
-      <c r="N156" s="10" t="str">
+      <c r="K156" s="16"/>
+      <c r="L156" s="16"/>
+      <c r="M156" s="16"/>
+      <c r="N156" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B156, $C$2:$C$636, C156, $D$2:$D$636, D156, $E$2:$E$636, E156) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
+      <c r="O156"/>
+      <c r="P156"/>
     </row>
     <row r="157" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="3">
@@ -8763,7 +8768,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="158" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A158" s="3">
         <v>46260.375694444447</v>
       </c>
@@ -8811,7 +8816,7 @@
       <c r="O158"/>
       <c r="P158" s="27"/>
     </row>
-    <row r="159" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A159" s="8" t="s">
         <v>61</v>
       </c>
@@ -8847,7 +8852,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="160" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A160" s="3">
         <v>46260.375</v>
       </c>
@@ -8932,52 +8937,47 @@
       <c r="P161"/>
     </row>
     <row r="162" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A162" s="3">
-        <v>46275.457638888889</v>
+      <c r="A162" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>19</v>
+        <v>114</v>
       </c>
       <c r="C162" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D162" s="4">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="E162" s="4">
-        <v>222</v>
+        <v>660</v>
       </c>
       <c r="F162" s="4">
-        <v>12.439222040000001</v>
+        <v>-20.948616600000001</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>39</v>
+        <v>115</v>
       </c>
       <c r="H162" s="5">
-        <v>197.44</v>
+        <v>834.9</v>
       </c>
       <c r="I162" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J162" s="64" t="s">
+      <c r="J162" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="K162" s="17" t="s">
-        <v>255</v>
-      </c>
-      <c r="L162" s="17">
-        <v>56375</v>
-      </c>
-      <c r="M162" s="17">
-        <f>ABS((D162*E162)-L162)</f>
-        <v>34175</v>
-      </c>
-      <c r="N162" s="10" t="str">
+      <c r="K162" s="16"/>
+      <c r="L162" s="16"/>
+      <c r="M162" s="16"/>
+      <c r="N162" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B162, $C$2:$C$636, C162, $D$2:$D$636, D162, $E$2:$E$636, E162) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-    </row>
-    <row r="163" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="O162"/>
+      <c r="P162"/>
+    </row>
+    <row r="163" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A163" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -9011,7 +9011,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="164" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A164" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -9145,7 +9145,7 @@
       </c>
       <c r="P166" s="27"/>
     </row>
-    <row r="167" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A167" s="3">
         <v>46259.388194444444</v>
       </c>
@@ -9191,7 +9191,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="168" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A168" s="42">
         <v>46293.375</v>
       </c>
@@ -9237,7 +9237,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="169" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A169" s="3">
         <v>46259.375</v>
       </c>
@@ -9323,7 +9323,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="171" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A171" s="11">
         <v>46252.688194444447</v>
       </c>
@@ -9359,7 +9359,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="172" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A172" s="11">
         <v>46252.645833333336</v>
       </c>
@@ -9394,7 +9394,7 @@
       </c>
       <c r="O172" s="22"/>
     </row>
-    <row r="173" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A173" s="8" t="s">
         <v>61</v>
       </c>
@@ -9430,7 +9430,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="174" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -9466,7 +9466,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="175" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A175" s="3">
         <v>46265.474999999999</v>
       </c>
@@ -9512,7 +9512,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="176" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A176" s="3">
         <v>46261.375694444447</v>
       </c>
@@ -9558,7 +9558,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="177" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A177" s="42">
         <v>46311.590277777781</v>
       </c>
@@ -9604,7 +9604,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="178" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A178" s="3">
         <v>46267.375</v>
       </c>
@@ -9650,7 +9650,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="179" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A179" s="8" t="s">
         <v>61</v>
       </c>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="P181" s="27"/>
     </row>
-    <row r="182" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A182" s="8" t="s">
         <v>61</v>
       </c>
@@ -9818,7 +9818,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="183" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A183" s="8" t="s">
         <v>61</v>
       </c>
@@ -9854,7 +9854,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="184" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A184" s="3">
         <v>46258.629861111112</v>
       </c>
@@ -9900,7 +9900,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="185" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A185" s="8" t="s">
         <v>61</v>
       </c>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="P185" s="27"/>
     </row>
-    <row r="186" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A186" s="3">
         <v>46294.475694444445</v>
       </c>
@@ -9983,7 +9983,7 @@
       <c r="O186" s="10"/>
       <c r="P186" s="10"/>
     </row>
-    <row r="187" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A187" s="8" t="s">
         <v>61</v>
       </c>
@@ -10024,7 +10024,7 @@
       <c r="O187" s="10"/>
       <c r="P187" s="10"/>
     </row>
-    <row r="188" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A188" s="8" t="s">
         <v>61</v>
       </c>
@@ -10060,7 +10060,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="189" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A189" s="3">
         <v>46260.375</v>
       </c>
@@ -10107,7 +10107,7 @@
       </c>
       <c r="P189" s="27"/>
     </row>
-    <row r="190" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A190" s="8" t="s">
         <v>61</v>
       </c>
@@ -10143,7 +10143,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="191" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A191" s="58">
         <v>46269.643055555556</v>
       </c>
@@ -10242,7 +10242,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="193" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A193" s="42">
         <v>46289.375694444447</v>
       </c>
@@ -10288,7 +10288,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="194" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A194" s="28">
         <v>46267.375</v>
       </c>
@@ -10334,7 +10334,7 @@
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="195" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A195" s="28">
         <v>46267.375</v>
       </c>
@@ -10529,7 +10529,7 @@
       </c>
       <c r="P198" s="27"/>
     </row>
-    <row r="199" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A199" s="8" t="s">
         <v>61</v>
       </c>
@@ -10563,7 +10563,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="200" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A200" s="8" t="s">
         <v>61</v>
       </c>
@@ -10597,7 +10597,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="201" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A201" s="8" t="s">
         <v>61</v>
       </c>
@@ -10686,7 +10686,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="203" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A203" s="3">
         <v>46265.460416666669</v>
       </c>
@@ -10734,45 +10734,52 @@
       <c r="P203" s="27"/>
     </row>
     <row r="204" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A204" s="6" t="s">
-        <v>61</v>
+      <c r="A204" s="3">
+        <v>46281.416666666664</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>15</v>
+        <v>267</v>
       </c>
       <c r="C204" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D204" s="4">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="E204" s="4">
-        <v>2435</v>
+        <v>726</v>
       </c>
       <c r="F204" s="4">
-        <v>16.69142665</v>
+        <v>-30.784631520000001</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>71</v>
+        <v>272</v>
       </c>
       <c r="H204" s="5">
-        <v>2086.6999999999998</v>
+        <v>1048.9000000000001</v>
       </c>
       <c r="I204" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J204" s="65" t="s">
-        <v>54</v>
-      </c>
-      <c r="K204" s="16"/>
-      <c r="L204" s="16"/>
-      <c r="M204" s="16"/>
-      <c r="N204" t="str">
+      <c r="J204" s="64" t="s">
+        <v>40</v>
+      </c>
+      <c r="K204" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="L204" s="17">
+        <v>17940</v>
+      </c>
+      <c r="M204" s="17">
+        <f>ABS((D204*E204)-L204)</f>
+        <v>10680</v>
+      </c>
+      <c r="N204" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B204, $C$2:$C$636, C204, $D$2:$D$636, D204, $E$2:$E$636, E204) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
     </row>
-    <row r="205" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A205" s="8" t="s">
         <v>61</v>
       </c>
@@ -10806,7 +10813,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="206" spans="1:16" s="27" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:16" s="27" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A206" s="11">
         <v>46252.6875</v>
       </c>
@@ -10846,7 +10853,7 @@
       </c>
       <c r="P206" s="10"/>
     </row>
-    <row r="207" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A207" s="8" t="s">
         <v>61</v>
       </c>
@@ -10885,7 +10892,7 @@
       <c r="O207" s="10"/>
       <c r="P207" s="10"/>
     </row>
-    <row r="208" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A208" s="48">
         <v>46302</v>
       </c>
@@ -10925,7 +10932,7 @@
       </c>
       <c r="O208"/>
     </row>
-    <row r="209" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A209" s="3">
         <v>46261.375694444447</v>
       </c>
@@ -10973,7 +10980,7 @@
       <c r="O209" s="10"/>
       <c r="P209" s="10"/>
     </row>
-    <row r="210" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A210" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -11019,7 +11026,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="211" spans="1:16" s="27" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:16" s="27" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A211" s="8" t="s">
         <v>61</v>
       </c>
@@ -11060,7 +11067,7 @@
       <c r="O211" s="10"/>
       <c r="P211" s="10"/>
     </row>
-    <row r="212" spans="1:16" s="27" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:16" s="27" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A212" s="8" t="s">
         <v>61</v>
       </c>
@@ -11099,7 +11106,7 @@
       <c r="O212" s="10"/>
       <c r="P212" s="10"/>
     </row>
-    <row r="213" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A213" s="28">
         <v>46258.443749999999</v>
       </c>
@@ -11147,7 +11154,7 @@
       <c r="O213" s="27"/>
       <c r="P213" s="27"/>
     </row>
-    <row r="214" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A214" s="38">
         <v>46253.4</v>
       </c>
@@ -11190,7 +11197,7 @@
       <c r="O214" s="27"/>
       <c r="P214" s="27"/>
     </row>
-    <row r="215" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A215" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -11236,7 +11243,7 @@
         <v>Unique</v>
       </c>
     </row>
-    <row r="216" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A216" s="3">
         <v>46275.375</v>
       </c>
@@ -11284,7 +11291,7 @@
       <c r="O216" s="10"/>
       <c r="P216" s="10"/>
     </row>
-    <row r="217" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A217" s="3">
         <v>46260.554861111108</v>
       </c>
@@ -11332,7 +11339,7 @@
       <c r="O217" s="10"/>
       <c r="P217" s="10"/>
     </row>
-    <row r="218" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A218" s="28">
         <v>46258.443055555559</v>
       </c>
@@ -11380,7 +11387,7 @@
       <c r="O218" s="27"/>
       <c r="P218" s="27"/>
     </row>
-    <row r="219" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A219" s="28">
         <v>46259.375</v>
       </c>
@@ -11428,7 +11435,7 @@
       <c r="O219" s="27"/>
       <c r="P219" s="27"/>
     </row>
-    <row r="220" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A220" s="8" t="s">
         <v>61</v>
       </c>
@@ -11465,7 +11472,7 @@
       </c>
       <c r="O220" s="27"/>
     </row>
-    <row r="221" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A221" s="8" t="s">
         <v>61</v>
       </c>
@@ -11500,46 +11507,52 @@
       </c>
     </row>
     <row r="222" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A222" s="6" t="s">
-        <v>61</v>
+      <c r="A222" s="3">
+        <v>46281.416666666664</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>15</v>
+        <v>267</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D222" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E222" s="4">
-        <v>2470</v>
+        <v>706</v>
       </c>
       <c r="F222" s="4">
-        <v>18.368716150000001</v>
+        <v>-32.691390980000001</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>71</v>
+        <v>272</v>
       </c>
       <c r="H222" s="5">
-        <v>2086.6999999999998</v>
+        <v>1048.9000000000001</v>
       </c>
       <c r="I222" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J222" s="65" t="s">
+      <c r="J222" s="64" t="s">
         <v>40</v>
       </c>
-      <c r="K222" s="16"/>
-      <c r="L222" s="16"/>
-      <c r="M222" s="16"/>
-      <c r="N222" t="str">
+      <c r="K222" s="17" t="s">
+        <v>269</v>
+      </c>
+      <c r="L222" s="17">
+        <v>17940</v>
+      </c>
+      <c r="M222" s="17">
+        <f>ABS((D222*E222)-L222)</f>
+        <v>10880</v>
+      </c>
+      <c r="N222" s="10" t="str">
         <f>IF(COUNTIFS( $B$2:$B$636, B222, $C$2:$C$636, C222, $D$2:$D$636, D222, $E$2:$E$636, E222) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
-      <c r="P222" s="22"/>
-    </row>
-    <row r="223" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="223" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A223" s="11">
         <v>46252.6875</v>
       </c>
@@ -11571,11 +11584,11 @@
         <v>116</v>
       </c>
       <c r="N223" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B223, $C$2:$C$636, C223, $D$2:$D$636, D223, $E$2:$E$636, E223) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="224" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" ref="N194:N257" si="0">IF(COUNTIFS( $B$2:$B$636, B223, $C$2:$C$636, C223, $D$2:$D$636, D223, $E$2:$E$636, E223) &gt; 1, "Duplicate", "Unique")</f>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="224" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A224" s="8" t="s">
         <v>61</v>
       </c>
@@ -11607,12 +11620,12 @@
         <v>116</v>
       </c>
       <c r="N224" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B224, $C$2:$C$636, C224, $D$2:$D$636, D224, $E$2:$E$636, E224) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="P224" s="27"/>
     </row>
-    <row r="225" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A225" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -11654,11 +11667,11 @@
         <v>275</v>
       </c>
       <c r="N225" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B225, $C$2:$C$636, C225, $D$2:$D$636, D225, $E$2:$E$636, E225) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="226" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="226" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A226" s="3">
         <v>46335.442361111112</v>
       </c>
@@ -11700,11 +11713,11 @@
         <v>500</v>
       </c>
       <c r="N226" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B226, $C$2:$C$636, C226, $D$2:$D$636, D226, $E$2:$E$636, E226) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="227" spans="1:16" s="27" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="227" spans="1:16" s="27" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A227" s="3">
         <v>46266.375</v>
       </c>
@@ -11746,13 +11759,13 @@
         <v>360</v>
       </c>
       <c r="N227" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B227, $C$2:$C$636, C227, $D$2:$D$636, D227, $E$2:$E$636, E227) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O227" s="10"/>
       <c r="P227" s="10"/>
     </row>
-    <row r="228" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:16" s="27" customFormat="1" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A228" s="11">
         <v>46252.645138888889</v>
       </c>
@@ -11787,13 +11800,13 @@
       <c r="L228" s="17"/>
       <c r="M228" s="17"/>
       <c r="N228" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B228, $C$2:$C$636, C228, $D$2:$D$636, D228, $E$2:$E$636, E228) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O228" s="10"/>
       <c r="P228" s="10"/>
     </row>
-    <row r="229" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A229" s="8" t="s">
         <v>61</v>
       </c>
@@ -11823,11 +11836,11 @@
       </c>
       <c r="J229" s="32"/>
       <c r="N229" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B229, $C$2:$C$636, C229, $D$2:$D$636, D229, $E$2:$E$636, E229) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="230" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="230" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A230" s="8" t="s">
         <v>61</v>
       </c>
@@ -11859,11 +11872,11 @@
         <v>117</v>
       </c>
       <c r="N230" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B230, $C$2:$C$636, C230, $D$2:$D$636, D230, $E$2:$E$636, E230) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="231" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="231" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A231" s="28">
         <v>46262.375</v>
       </c>
@@ -11905,13 +11918,13 @@
         <v>320</v>
       </c>
       <c r="N231" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B231, $C$2:$C$636, C231, $D$2:$D$636, D231, $E$2:$E$636, E231) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O231" s="27"/>
       <c r="P231" s="27"/>
     </row>
-    <row r="232" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A232" s="28">
         <v>46265.486111111109</v>
       </c>
@@ -11953,13 +11966,13 @@
         <v>448</v>
       </c>
       <c r="N232" s="26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B232, $C$2:$C$636, C232, $D$2:$D$636, D232, $E$2:$E$636, E232) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O232" s="27"/>
       <c r="P232" s="27"/>
     </row>
-    <row r="233" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A233" s="3">
         <v>46276.4</v>
       </c>
@@ -12001,11 +12014,11 @@
         <v>500</v>
       </c>
       <c r="N233" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B233, $C$2:$C$636, C233, $D$2:$D$636, D233, $E$2:$E$636, E233) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="234" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="234" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A234" s="8" t="s">
         <v>61</v>
       </c>
@@ -12037,11 +12050,11 @@
         <v>117</v>
       </c>
       <c r="N234" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B234, $C$2:$C$636, C234, $D$2:$D$636, D234, $E$2:$E$636, E234) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="235" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="235" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A235" s="8" t="s">
         <v>61</v>
       </c>
@@ -12071,11 +12084,11 @@
       </c>
       <c r="J235" s="32"/>
       <c r="N235" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B235, $C$2:$C$636, C235, $D$2:$D$636, D235, $E$2:$E$636, E235) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="236" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="236" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A236" s="8" t="s">
         <v>61</v>
       </c>
@@ -12105,12 +12118,12 @@
       </c>
       <c r="J236" s="32"/>
       <c r="N236" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B236, $C$2:$C$636, C236, $D$2:$D$636, D236, $E$2:$E$636, E236) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O236" s="27"/>
     </row>
-    <row r="237" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A237" s="3">
         <v>46276.375</v>
       </c>
@@ -12152,11 +12165,11 @@
         <v>816</v>
       </c>
       <c r="N237" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B237, $C$2:$C$636, C237, $D$2:$D$636, D237, $E$2:$E$636, E237) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="238" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="238" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A238" s="28">
         <v>46260.556944444441</v>
       </c>
@@ -12198,11 +12211,11 @@
         <v>150</v>
       </c>
       <c r="N238" s="26" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B238, $C$2:$C$636, C238, $D$2:$D$636, D238, $E$2:$E$636, E238) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="239" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A239" s="28">
         <v>46261.375</v>
       </c>
@@ -12244,11 +12257,11 @@
         <v>250</v>
       </c>
       <c r="N239" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B239, $C$2:$C$636, C239, $D$2:$D$636, D239, $E$2:$E$636, E239) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
     </row>
-    <row r="240" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A240" s="3">
         <v>46269.614583333336</v>
       </c>
@@ -12290,7 +12303,7 @@
         <v>280</v>
       </c>
       <c r="N240" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B240, $C$2:$C$636, C240, $D$2:$D$636, D240, $E$2:$E$636, E240) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -12336,14 +12349,14 @@
         <v>800</v>
       </c>
       <c r="N241" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B241, $C$2:$C$636, C241, $D$2:$D$636, D241, $E$2:$E$636, E241) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O241" s="36" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="242" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A242" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -12375,11 +12388,11 @@
         <v>54</v>
       </c>
       <c r="N242" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B242, $C$2:$C$636, C242, $D$2:$D$636, D242, $E$2:$E$636, E242) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="243" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="243" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A243" s="3">
         <v>46294.375</v>
       </c>
@@ -12421,11 +12434,11 @@
         <v>300</v>
       </c>
       <c r="N243" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B243, $C$2:$C$636, C243, $D$2:$D$636, D243, $E$2:$E$636, E243) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="244" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="244" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A244" s="3">
         <v>46266.375694444447</v>
       </c>
@@ -12467,11 +12480,11 @@
         <v>300</v>
       </c>
       <c r="N244" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B244, $C$2:$C$636, C244, $D$2:$D$636, D244, $E$2:$E$636, E244) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="245" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="245" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A245" s="3">
         <v>46261.375</v>
       </c>
@@ -12513,11 +12526,11 @@
         <v>260</v>
       </c>
       <c r="N245" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B245, $C$2:$C$636, C245, $D$2:$D$636, D245, $E$2:$E$636, E245) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="246" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="246" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A246" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -12559,11 +12572,11 @@
         <v>400</v>
       </c>
       <c r="N246" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B246, $C$2:$C$636, C246, $D$2:$D$636, D246, $E$2:$E$636, E246) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="247" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="247" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A247" s="3">
         <v>46276.390277777777</v>
       </c>
@@ -12605,11 +12618,11 @@
         <v>500</v>
       </c>
       <c r="N247" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B247, $C$2:$C$636, C247, $D$2:$D$636, D247, $E$2:$E$636, E247) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="248" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="248" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A248" s="11">
         <v>46252.6875</v>
       </c>
@@ -12641,11 +12654,11 @@
         <v>117</v>
       </c>
       <c r="N248" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B248, $C$2:$C$636, C248, $D$2:$D$636, D248, $E$2:$E$636, E248) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="249" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="249" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A249" s="8" t="s">
         <v>61</v>
       </c>
@@ -12675,11 +12688,11 @@
       </c>
       <c r="J249" s="32"/>
       <c r="N249" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B249, $C$2:$C$636, C249, $D$2:$D$636, D249, $E$2:$E$636, E249) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="250" spans="1:16" s="27" customFormat="1" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="250" spans="1:16" s="27" customFormat="1" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A250" s="31">
         <v>46255</v>
       </c>
@@ -12721,12 +12734,12 @@
         <v>140</v>
       </c>
       <c r="N250" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B250, $C$2:$C$636, C250, $D$2:$D$636, D250, $E$2:$E$636, E250) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
       <c r="O250" s="10"/>
     </row>
-    <row r="251" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A251" s="28">
         <v>46261.385416666664</v>
       </c>
@@ -12768,7 +12781,7 @@
         <v>300</v>
       </c>
       <c r="N251" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B251, $C$2:$C$636, C251, $D$2:$D$636, D251, $E$2:$E$636, E251) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Duplicate</v>
       </c>
     </row>
@@ -12814,7 +12827,7 @@
         <v>48320</v>
       </c>
       <c r="N252" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B252, $C$2:$C$636, C252, $D$2:$D$636, D252, $E$2:$E$636, E252) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O252" s="36" t="s">
@@ -12822,7 +12835,7 @@
       </c>
       <c r="P252" s="10"/>
     </row>
-    <row r="253" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A253" s="42">
         <v>46304.375</v>
       </c>
@@ -12864,11 +12877,11 @@
         <v>1000</v>
       </c>
       <c r="N253" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B253, $C$2:$C$636, C253, $D$2:$D$636, D253, $E$2:$E$636, E253) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="254" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="254" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A254" s="8" t="s">
         <v>61</v>
       </c>
@@ -12898,11 +12911,11 @@
       </c>
       <c r="J254" s="32"/>
       <c r="N254" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B254, $C$2:$C$636, C254, $D$2:$D$636, D254, $E$2:$E$636, E254) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="255" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="255" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A255" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -12937,11 +12950,11 @@
         <v>144</v>
       </c>
       <c r="N255" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B255, $C$2:$C$636, C255, $D$2:$D$636, D255, $E$2:$E$636, E255) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="256" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="0"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="256" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A256" s="19">
         <v>46255</v>
       </c>
@@ -12983,7 +12996,7 @@
         <v>300</v>
       </c>
       <c r="N256" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B256, $C$2:$C$636, C256, $D$2:$D$636, D256, $E$2:$E$636, E256) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13029,7 +13042,7 @@
         <v>300</v>
       </c>
       <c r="N257" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B257, $C$2:$C$636, C257, $D$2:$D$636, D257, $E$2:$E$636, E257) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="0"/>
         <v>Unique</v>
       </c>
       <c r="O257" s="36" t="s">
@@ -13037,7 +13050,7 @@
       </c>
       <c r="P257" s="27"/>
     </row>
-    <row r="258" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A258" s="8" t="s">
         <v>61</v>
       </c>
@@ -13067,12 +13080,12 @@
       </c>
       <c r="J258" s="32"/>
       <c r="N258" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B258, $C$2:$C$636, C258, $D$2:$D$636, D258, $E$2:$E$636, E258) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" ref="N258:N316" si="1">IF(COUNTIFS( $B$2:$B$636, B258, $C$2:$C$636, C258, $D$2:$D$636, D258, $E$2:$E$636, E258) &gt; 1, "Duplicate", "Unique")</f>
         <v>Unique</v>
       </c>
       <c r="P258" s="27"/>
     </row>
-    <row r="259" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A259" s="8" t="s">
         <v>61</v>
       </c>
@@ -13104,11 +13117,11 @@
         <v>116</v>
       </c>
       <c r="N259" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B259, $C$2:$C$636, C259, $D$2:$D$636, D259, $E$2:$E$636, E259) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="260" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="260" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A260" s="3">
         <v>46272.375694444447</v>
       </c>
@@ -13150,12 +13163,12 @@
         <v>250</v>
       </c>
       <c r="N260" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B260, $C$2:$C$636, C260, $D$2:$D$636, D260, $E$2:$E$636, E260) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P260" s="27"/>
     </row>
-    <row r="261" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A261" s="3">
         <v>46276.388194444444</v>
       </c>
@@ -13197,11 +13210,11 @@
         <v>450</v>
       </c>
       <c r="N261" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B261, $C$2:$C$636, C261, $D$2:$D$636, D261, $E$2:$E$636, E261) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="262" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="262" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A262" s="3">
         <v>46262.375</v>
       </c>
@@ -13243,12 +13256,12 @@
         <v>370</v>
       </c>
       <c r="N262" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B262, $C$2:$C$636, C262, $D$2:$D$636, D262, $E$2:$E$636, E262) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P262" s="27"/>
     </row>
-    <row r="263" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A263" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -13278,12 +13291,12 @@
       </c>
       <c r="J263" s="32"/>
       <c r="N263" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B263, $C$2:$C$636, C263, $D$2:$D$636, D263, $E$2:$E$636, E263) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O263" s="27"/>
     </row>
-    <row r="264" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A264" s="8" t="s">
         <v>61</v>
       </c>
@@ -13315,7 +13328,7 @@
         <v>117</v>
       </c>
       <c r="N264" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B264, $C$2:$C$636, C264, $D$2:$D$636, D264, $E$2:$E$636, E264) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13361,14 +13374,14 @@
         <v>47900</v>
       </c>
       <c r="N265" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B265, $C$2:$C$636, C265, $D$2:$D$636, D265, $E$2:$E$636, E265) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O265" s="36" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="266" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A266" s="8" t="s">
         <v>61</v>
       </c>
@@ -13398,7 +13411,7 @@
       </c>
       <c r="J266" s="32"/>
       <c r="N266" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B266, $C$2:$C$636, C266, $D$2:$D$636, D266, $E$2:$E$636, E266) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13440,11 +13453,11 @@
         <v>25300</v>
       </c>
       <c r="M267" s="17">
-        <f>ABS((D267*E267)-L267)</f>
+        <f t="shared" ref="M267:M272" si="2">ABS((D267*E267)-L267)</f>
         <v>650</v>
       </c>
       <c r="N267" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B267, $C$2:$C$636, C267, $D$2:$D$636, D267, $E$2:$E$636, E267) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O267" s="36" t="s">
@@ -13489,18 +13502,18 @@
         <v>12480</v>
       </c>
       <c r="M268" s="17">
-        <f>ABS((D268*E268)-L268)</f>
+        <f t="shared" si="2"/>
         <v>495</v>
       </c>
       <c r="N268" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B268, $C$2:$C$636, C268, $D$2:$D$636, D268, $E$2:$E$636, E268) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O268" s="36" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="269" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A269" s="3">
         <v>46290.385416666664</v>
       </c>
@@ -13538,11 +13551,11 @@
         <v>4200</v>
       </c>
       <c r="M269" s="17">
-        <f>ABS((D269*E269)-L269)</f>
+        <f t="shared" si="2"/>
         <v>290</v>
       </c>
       <c r="N269" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B269, $C$2:$C$636, C269, $D$2:$D$636, D269, $E$2:$E$636, E269) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -13584,11 +13597,11 @@
         <v>25780</v>
       </c>
       <c r="M270" s="17">
-        <f>ABS((D270*E270)-L270)</f>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N270" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B270, $C$2:$C$636, C270, $D$2:$D$636, D270, $E$2:$E$636, E270) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O270" s="36" t="s">
@@ -13596,7 +13609,7 @@
       </c>
       <c r="P270"/>
     </row>
-    <row r="271" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A271" s="3">
         <v>46262.375</v>
       </c>
@@ -13634,15 +13647,15 @@
         <v>13300</v>
       </c>
       <c r="M271" s="17">
-        <f>ABS((D271*E271)-L271)</f>
+        <f t="shared" si="2"/>
         <v>300</v>
       </c>
       <c r="N271" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B271, $C$2:$C$636, C271, $D$2:$D$636, D271, $E$2:$E$636, E271) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="272" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="272" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A272" s="3">
         <v>46268.375</v>
       </c>
@@ -13680,15 +13693,15 @@
         <v>25800</v>
       </c>
       <c r="M272" s="17">
-        <f>ABS((D272*E272)-L272)</f>
+        <f t="shared" si="2"/>
         <v>1800</v>
       </c>
       <c r="N272" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B272, $C$2:$C$636, C272, $D$2:$D$636, D272, $E$2:$E$636, E272) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="273" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="273" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A273" s="8" t="s">
         <v>61</v>
       </c>
@@ -13720,11 +13733,11 @@
         <v>116</v>
       </c>
       <c r="N273" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B273, $C$2:$C$636, C273, $D$2:$D$636, D273, $E$2:$E$636, E273) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="274" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="274" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A274" s="3">
         <v>46265.390277777777</v>
       </c>
@@ -13766,13 +13779,13 @@
         <v>650</v>
       </c>
       <c r="N274" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B274, $C$2:$C$636, C274, $D$2:$D$636, D274, $E$2:$E$636, E274) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O274"/>
       <c r="P274"/>
     </row>
-    <row r="275" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A275" s="8" t="s">
         <v>61</v>
       </c>
@@ -13804,11 +13817,11 @@
         <v>116</v>
       </c>
       <c r="N275" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B275, $C$2:$C$636, C275, $D$2:$D$636, D275, $E$2:$E$636, E275) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="276" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="276" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A276" s="8" t="s">
         <v>61</v>
       </c>
@@ -13840,11 +13853,11 @@
         <v>116</v>
       </c>
       <c r="N276" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B276, $C$2:$C$636, C276, $D$2:$D$636, D276, $E$2:$E$636, E276) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="277" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="277" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A277" s="3">
         <v>46275.507638888892</v>
       </c>
@@ -13886,11 +13899,11 @@
         <v>47480</v>
       </c>
       <c r="N277" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B277, $C$2:$C$636, C277, $D$2:$D$636, D277, $E$2:$E$636, E277) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="278" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="278" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A278" s="3">
         <v>46276.375</v>
       </c>
@@ -13932,11 +13945,11 @@
         <v>450</v>
       </c>
       <c r="N278" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B278, $C$2:$C$636, C278, $D$2:$D$636, D278, $E$2:$E$636, E278) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="279" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="279" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A279" s="3">
         <v>46290.385416666664</v>
       </c>
@@ -13978,11 +13991,11 @@
         <v>420</v>
       </c>
       <c r="N279" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B279, $C$2:$C$636, C279, $D$2:$D$636, D279, $E$2:$E$636, E279) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="280" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="280" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A280" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -14024,11 +14037,11 @@
         <v>340</v>
       </c>
       <c r="N280" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B280, $C$2:$C$636, C280, $D$2:$D$636, D280, $E$2:$E$636, E280) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="281" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="281" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A281" s="3">
         <v>46262.463194444441</v>
       </c>
@@ -14070,11 +14083,11 @@
         <v>300</v>
       </c>
       <c r="N281" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B281, $C$2:$C$636, C281, $D$2:$D$636, D281, $E$2:$E$636, E281) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="282" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="282" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A282" s="8" t="s">
         <v>61</v>
       </c>
@@ -14106,11 +14119,11 @@
         <v>116</v>
       </c>
       <c r="N282" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B282, $C$2:$C$636, C282, $D$2:$D$636, D282, $E$2:$E$636, E282) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="283" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="283" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A283" s="8" t="s">
         <v>61</v>
       </c>
@@ -14140,11 +14153,11 @@
       </c>
       <c r="J283" s="32"/>
       <c r="N283" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B283, $C$2:$C$636, C283, $D$2:$D$636, D283, $E$2:$E$636, E283) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="284" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="284" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A284" s="3">
         <v>46262.375</v>
       </c>
@@ -14186,11 +14199,11 @@
         <v>300</v>
       </c>
       <c r="N284" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B284, $C$2:$C$636, C284, $D$2:$D$636, D284, $E$2:$E$636, E284) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="285" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="285" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A285" s="8" t="s">
         <v>61</v>
       </c>
@@ -14222,11 +14235,11 @@
         <v>116</v>
       </c>
       <c r="N285" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B285, $C$2:$C$636, C285, $D$2:$D$636, D285, $E$2:$E$636, E285) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="286" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="286" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A286" s="3">
         <v>46260.634027777778</v>
       </c>
@@ -14268,11 +14281,11 @@
         <v>480</v>
       </c>
       <c r="N286" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B286, $C$2:$C$636, C286, $D$2:$D$636, D286, $E$2:$E$636, E286) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="287" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="287" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A287" s="48">
         <v>46302</v>
       </c>
@@ -14307,12 +14320,12 @@
       <c r="L287" s="16"/>
       <c r="M287" s="16"/>
       <c r="N287" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B287, $C$2:$C$636, C287, $D$2:$D$636, D287, $E$2:$E$636, E287) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O287"/>
     </row>
-    <row r="288" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A288" s="3">
         <v>46260.375</v>
       </c>
@@ -14354,11 +14367,11 @@
         <v>300</v>
       </c>
       <c r="N288" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B288, $C$2:$C$636, C288, $D$2:$D$636, D288, $E$2:$E$636, E288) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="289" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="289" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A289" s="8" t="s">
         <v>61</v>
       </c>
@@ -14390,11 +14403,11 @@
         <v>117</v>
       </c>
       <c r="N289" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B289, $C$2:$C$636, C289, $D$2:$D$636, D289, $E$2:$E$636, E289) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="290" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="290" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A290" s="8" t="s">
         <v>61</v>
       </c>
@@ -14426,11 +14439,11 @@
         <v>116</v>
       </c>
       <c r="N290" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B290, $C$2:$C$636, C290, $D$2:$D$636, D290, $E$2:$E$636, E290) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="291" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="291" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A291" s="3">
         <v>46254.642361111109</v>
       </c>
@@ -14467,11 +14480,11 @@
       <c r="L291" s="16"/>
       <c r="M291" s="16"/>
       <c r="N291" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B291, $C$2:$C$636, C291, $D$2:$D$636, D291, $E$2:$E$636, E291) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="292" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="292" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A292" s="8" t="s">
         <v>61</v>
       </c>
@@ -14503,11 +14516,11 @@
         <v>116</v>
       </c>
       <c r="N292" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B292, $C$2:$C$636, C292, $D$2:$D$636, D292, $E$2:$E$636, E292) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="293" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="293" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A293" s="8" t="s">
         <v>61</v>
       </c>
@@ -14539,11 +14552,11 @@
         <v>117</v>
       </c>
       <c r="N293" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B293, $C$2:$C$636, C293, $D$2:$D$636, D293, $E$2:$E$636, E293) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="294" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="294" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A294" s="3">
         <v>46265.415277777778</v>
       </c>
@@ -14585,11 +14598,11 @@
         <v>285</v>
       </c>
       <c r="N294" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B294, $C$2:$C$636, C294, $D$2:$D$636, D294, $E$2:$E$636, E294) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="295" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="295" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A295" s="3">
         <v>46266.375</v>
       </c>
@@ -14631,11 +14644,11 @@
         <v>726</v>
       </c>
       <c r="N295" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B295, $C$2:$C$636, C295, $D$2:$D$636, D295, $E$2:$E$636, E295) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="296" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="296" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A296" s="11">
         <v>46252.6875</v>
       </c>
@@ -14667,11 +14680,11 @@
         <v>152</v>
       </c>
       <c r="N296" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B296, $C$2:$C$636, C296, $D$2:$D$636, D296, $E$2:$E$636, E296) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="297" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="297" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A297" s="11">
         <v>46252.6875</v>
       </c>
@@ -14703,11 +14716,11 @@
         <v>116</v>
       </c>
       <c r="N297" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B297, $C$2:$C$636, C297, $D$2:$D$636, D297, $E$2:$E$636, E297) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="298" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="298" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A298" s="8" t="s">
         <v>61</v>
       </c>
@@ -14737,11 +14750,11 @@
       </c>
       <c r="J298" s="32"/>
       <c r="N298" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B298, $C$2:$C$636, C298, $D$2:$D$636, D298, $E$2:$E$636, E298) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="299" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="299" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A299" s="3">
         <v>46265.375694444447</v>
       </c>
@@ -14783,11 +14796,11 @@
         <v>275</v>
       </c>
       <c r="N299" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B299, $C$2:$C$636, C299, $D$2:$D$636, D299, $E$2:$E$636, E299) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="300" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="300" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A300" s="3">
         <v>46269.375</v>
       </c>
@@ -14829,11 +14842,11 @@
         <v>250</v>
       </c>
       <c r="N300" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B300, $C$2:$C$636, C300, $D$2:$D$636, D300, $E$2:$E$636, E300) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="301" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="301" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A301" s="3">
         <v>46290.385416666664</v>
       </c>
@@ -14875,11 +14888,11 @@
         <v>250</v>
       </c>
       <c r="N301" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B301, $C$2:$C$636, C301, $D$2:$D$636, D301, $E$2:$E$636, E301) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="302" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="302" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A302" s="8" t="s">
         <v>61</v>
       </c>
@@ -14909,11 +14922,11 @@
       </c>
       <c r="J302" s="32"/>
       <c r="N302" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B302, $C$2:$C$636, C302, $D$2:$D$636, D302, $E$2:$E$636, E302) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="303" spans="1:16" ht="40.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="303" spans="1:16" ht="40.799999999999997" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A303" s="3">
         <v>46260.557638888888</v>
       </c>
@@ -14955,12 +14968,12 @@
         <v>250</v>
       </c>
       <c r="N303" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B303, $C$2:$C$636, C303, $D$2:$D$636, D303, $E$2:$E$636, E303) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="P303" s="27"/>
     </row>
-    <row r="304" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A304" s="8" t="s">
         <v>61</v>
       </c>
@@ -14990,11 +15003,11 @@
       </c>
       <c r="J304" s="32"/>
       <c r="N304" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B304, $C$2:$C$636, C304, $D$2:$D$636, D304, $E$2:$E$636, E304) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="305" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="305" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A305" s="8" t="s">
         <v>61</v>
       </c>
@@ -15024,11 +15037,11 @@
       </c>
       <c r="J305" s="32"/>
       <c r="N305" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B305, $C$2:$C$636, C305, $D$2:$D$636, D305, $E$2:$E$636, E305) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="306" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="306" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A306" s="8" t="s">
         <v>61</v>
       </c>
@@ -15058,11 +15071,11 @@
       </c>
       <c r="J306" s="32"/>
       <c r="N306" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B306, $C$2:$C$636, C306, $D$2:$D$636, D306, $E$2:$E$636, E306) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="307" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="307" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A307" s="3">
         <v>46260.550694444442</v>
       </c>
@@ -15104,11 +15117,11 @@
         <v>300</v>
       </c>
       <c r="N307" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B307, $C$2:$C$636, C307, $D$2:$D$636, D307, $E$2:$E$636, E307) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="308" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="308" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A308" s="11">
         <v>46252.635416666664</v>
       </c>
@@ -15140,11 +15153,11 @@
         <v>54</v>
       </c>
       <c r="N308" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B308, $C$2:$C$636, C308, $D$2:$D$636, D308, $E$2:$E$636, E308) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="309" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="309" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A309" s="11">
         <v>46252.6875</v>
       </c>
@@ -15176,11 +15189,11 @@
         <v>117</v>
       </c>
       <c r="N309" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B309, $C$2:$C$636, C309, $D$2:$D$636, D309, $E$2:$E$636, E309) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="310" spans="1:16" ht="40.799999999999997" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="310" spans="1:16" ht="40.799999999999997" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A310" s="3">
         <v>46258.375694444447</v>
       </c>
@@ -15222,11 +15235,11 @@
         <v>235</v>
       </c>
       <c r="N310" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B310, $C$2:$C$636, C310, $D$2:$D$636, D310, $E$2:$E$636, E310) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="311" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="311" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A311" s="11">
         <v>46252.6875</v>
       </c>
@@ -15258,11 +15271,11 @@
         <v>117</v>
       </c>
       <c r="N311" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B311, $C$2:$C$636, C311, $D$2:$D$636, D311, $E$2:$E$636, E311) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="312" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="312" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A312" s="9" t="s">
         <v>61</v>
       </c>
@@ -15292,11 +15305,11 @@
       </c>
       <c r="J312" s="32"/>
       <c r="N312" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B312, $C$2:$C$636, C312, $D$2:$D$636, D312, $E$2:$E$636, E312) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="313" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="313" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A313" s="39" t="s">
         <v>61</v>
       </c>
@@ -15331,13 +15344,13 @@
       <c r="L313" s="25"/>
       <c r="M313" s="25"/>
       <c r="N313" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B313, $C$2:$C$636, C313, $D$2:$D$636, D313, $E$2:$E$636, E313) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O313" s="27"/>
       <c r="P313" s="27"/>
     </row>
-    <row r="314" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A314" s="38">
         <v>46251.506249999999</v>
       </c>
@@ -15372,13 +15385,13 @@
       <c r="L314" s="25"/>
       <c r="M314" s="25"/>
       <c r="N314" s="27" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B314, $C$2:$C$636, C314, $D$2:$D$636, D314, $E$2:$E$636, E314) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
       <c r="O314" s="27"/>
       <c r="P314" s="27"/>
     </row>
-    <row r="315" spans="1:16" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:16" ht="27.6" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A315" s="3">
         <v>46259.532638888886</v>
       </c>
@@ -15420,11 +15433,11 @@
         <v>250</v>
       </c>
       <c r="N315" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B315, $C$2:$C$636, C315, $D$2:$D$636, D315, $E$2:$E$636, E315) &gt; 1, "Duplicate", "Unique")</f>
-        <v>Unique</v>
-      </c>
-    </row>
-    <row r="316" spans="1:16" ht="27.6" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>Unique</v>
+      </c>
+    </row>
+    <row r="316" spans="1:16" ht="27.6" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A316" s="8" t="s">
         <v>61</v>
       </c>
@@ -15456,7 +15469,7 @@
         <v>116</v>
       </c>
       <c r="N316" s="10" t="str">
-        <f>IF(COUNTIFS( $B$2:$B$636, B316, $C$2:$C$636, C316, $D$2:$D$636, D316, $E$2:$E$636, E316) &gt; 1, "Duplicate", "Unique")</f>
+        <f t="shared" si="1"/>
         <v>Unique</v>
       </c>
     </row>
@@ -22779,14 +22792,19 @@
   <autoFilter ref="A1:P316">
     <filterColumn colId="2">
       <filters>
-        <filter val="S"/>
+        <filter val="B"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="9">
+      <filters>
+        <filter val="SSBO"/>
       </filters>
     </filterColumn>
     <filterColumn colId="14">
       <filters blank="1"/>
     </filterColumn>
-    <sortState ref="A2:P316">
-      <sortCondition ref="F1"/>
+    <sortState ref="A2:P222">
+      <sortCondition descending="1" ref="F1:F316"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="7" type="noConversion"/>
